--- a/research/traditional_assets/database/data/bahrain/bahrain_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_metals_mining.xlsx
@@ -1127,43 +1127,43 @@
         <v>4.86818181818182</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>172.563874637149</v>
       </c>
       <c r="G2">
         <v>1.67425764679616</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0712212547443626</v>
       </c>
       <c r="I2">
         <v>0.235078369905956</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>4880.2</v>
       </c>
       <c r="L2">
-        <v>7147.15817860331</v>
+        <v>7080.63054798922</v>
       </c>
       <c r="M2">
         <v>6200.2</v>
       </c>
       <c r="N2">
-        <v>6967.35817860331</v>
+        <v>6964.63054798922</v>
       </c>
       <c r="O2">
         <v>1499.8</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>63.8</v>
       </c>
       <c r="Q2">
         <v>0.174918204913988</v>
       </c>
       <c r="R2">
-        <v>0.160701326096054</v>
+        <v>0.160746326096054</v>
       </c>
       <c r="S2">
         <v>0.106277188197372</v>
@@ -1185,13 +1185,13 @@
         <v>0.196013200379662</v>
       </c>
       <c r="X2">
-        <v>0.160701326096054</v>
+        <v>0.16186194555157</v>
       </c>
       <c r="Y2">
         <v>1.28669378736785</v>
       </c>
       <c r="Z2">
-        <v>0.984219909265296</v>
+        <v>0.9941615245104</v>
       </c>
       <c r="AA2">
         <v>1499.8</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1607013260960539</v>
+        <v>0.160746326096054</v>
       </c>
       <c r="C2">
-        <v>7147.158178603309</v>
+        <v>7080.630547989215</v>
       </c>
       <c r="D2">
-        <v>6967.358178603309</v>
+        <v>6964.630547989215</v>
       </c>
       <c r="E2">
-        <v>-1499.8</v>
+        <v>-1436</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>63.8</v>
       </c>
       <c r="G2">
         <v>179.8</v>
@@ -1445,28 +1445,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.20914</v>
       </c>
       <c r="N2">
-        <v>553.7816326530613</v>
+        <v>550.5724926530612</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>553.7816326530613</v>
+        <v>550.5724926530612</v>
       </c>
       <c r="Q2">
-        <v>914.0816326530612</v>
+        <v>910.8724926530612</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1607013260960539</v>
+        <v>0.1618619455515697</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652959</v>
+        <v>0.9941615245104</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>172.5638746371493</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.160746326096054</v>
+        <v>0.160791326096054</v>
       </c>
       <c r="C3">
-        <v>7080.630547989215</v>
+        <v>7014.105052203579</v>
       </c>
       <c r="D3">
-        <v>6964.630547989215</v>
+        <v>6961.90505220358</v>
       </c>
       <c r="E3">
-        <v>-1436</v>
+        <v>-1372.2</v>
       </c>
       <c r="F3">
-        <v>63.8</v>
+        <v>127.6</v>
       </c>
       <c r="G3">
         <v>179.8</v>
@@ -1527,28 +1527,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M3">
-        <v>3.20914</v>
+        <v>6.41828</v>
       </c>
       <c r="N3">
-        <v>550.5724926530612</v>
+        <v>547.3633526530613</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>550.5724926530612</v>
+        <v>547.3633526530613</v>
       </c>
       <c r="Q3">
-        <v>910.8724926530612</v>
+        <v>907.6633526530612</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1618619455515697</v>
+        <v>0.1630462511184224</v>
       </c>
       <c r="T3">
-        <v>0.9941615245104</v>
+        <v>1.004306029862547</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>172.5638746371493</v>
+        <v>86.28193731857465</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.160791326096054</v>
+        <v>0.1608363260960539</v>
       </c>
       <c r="C4">
-        <v>7014.105052203579</v>
+        <v>6947.581688741091</v>
       </c>
       <c r="D4">
-        <v>6961.90505220358</v>
+        <v>6959.181688741091</v>
       </c>
       <c r="E4">
-        <v>-1372.2</v>
+        <v>-1308.4</v>
       </c>
       <c r="F4">
-        <v>127.6</v>
+        <v>191.4</v>
       </c>
       <c r="G4">
         <v>179.8</v>
@@ -1609,28 +1609,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M4">
-        <v>6.41828</v>
+        <v>9.627419999999999</v>
       </c>
       <c r="N4">
-        <v>547.3633526530613</v>
+        <v>544.1542126530612</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>547.3633526530613</v>
+        <v>544.1542126530612</v>
       </c>
       <c r="Q4">
-        <v>907.6633526530612</v>
+        <v>904.4542126530612</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1630462511184224</v>
+        <v>0.1642549753567566</v>
       </c>
       <c r="T4">
-        <v>1.004306029862547</v>
+        <v>1.014659700273501</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>86.28193731857465</v>
+        <v>57.52129154571643</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1608363260960539</v>
+        <v>0.1608813260960539</v>
       </c>
       <c r="C5">
-        <v>6947.581688741091</v>
+        <v>6881.060455100352</v>
       </c>
       <c r="D5">
-        <v>6959.181688741091</v>
+        <v>6956.460455100351</v>
       </c>
       <c r="E5">
-        <v>-1308.4</v>
+        <v>-1244.6</v>
       </c>
       <c r="F5">
-        <v>191.4</v>
+        <v>255.2</v>
       </c>
       <c r="G5">
         <v>179.8</v>
@@ -1691,28 +1691,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M5">
-        <v>9.627419999999999</v>
+        <v>12.83656</v>
       </c>
       <c r="N5">
-        <v>544.1542126530612</v>
+        <v>540.9450726530613</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>544.1542126530612</v>
+        <v>540.9450726530613</v>
       </c>
       <c r="Q5">
-        <v>904.4542126530612</v>
+        <v>901.2450726530612</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1642549753567566</v>
+        <v>0.1654888813500562</v>
       </c>
       <c r="T5">
-        <v>1.014659700273501</v>
+        <v>1.02522907215135</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>57.52129154571643</v>
+        <v>43.14096865928732</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1608813260960539</v>
+        <v>0.1609263260960539</v>
       </c>
       <c r="C6">
-        <v>6881.060455100352</v>
+        <v>6814.541348783884</v>
       </c>
       <c r="D6">
-        <v>6956.460455100351</v>
+        <v>6953.741348783884</v>
       </c>
       <c r="E6">
-        <v>-1244.6</v>
+        <v>-1180.8</v>
       </c>
       <c r="F6">
-        <v>255.2</v>
+        <v>319</v>
       </c>
       <c r="G6">
         <v>179.8</v>
@@ -1773,28 +1773,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M6">
-        <v>12.83656</v>
+        <v>16.0457</v>
       </c>
       <c r="N6">
-        <v>540.9450726530613</v>
+        <v>537.7359326530612</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>540.9450726530613</v>
+        <v>537.7359326530612</v>
       </c>
       <c r="Q6">
-        <v>901.2450726530612</v>
+        <v>898.0359326530612</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1654888813500562</v>
+        <v>0.1667487643116357</v>
       </c>
       <c r="T6">
-        <v>1.02522907215135</v>
+        <v>1.036020957121364</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.14096865928732</v>
+        <v>34.51277492742985</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1609263260960539</v>
+        <v>0.1609713260960539</v>
       </c>
       <c r="C7">
-        <v>6814.541348783884</v>
+        <v>6748.024367298106</v>
       </c>
       <c r="D7">
-        <v>6953.741348783884</v>
+        <v>6951.024367298106</v>
       </c>
       <c r="E7">
-        <v>-1180.8</v>
+        <v>-1117</v>
       </c>
       <c r="F7">
-        <v>319</v>
+        <v>382.8</v>
       </c>
       <c r="G7">
         <v>179.8</v>
@@ -1855,28 +1855,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M7">
-        <v>16.0457</v>
+        <v>19.25484</v>
       </c>
       <c r="N7">
-        <v>537.7359326530612</v>
+        <v>534.5267926530613</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>537.7359326530612</v>
+        <v>534.5267926530613</v>
       </c>
       <c r="Q7">
-        <v>898.0359326530612</v>
+        <v>894.8267926530613</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1667487643116357</v>
+        <v>0.1680354532936744</v>
       </c>
       <c r="T7">
-        <v>1.036020957121364</v>
+        <v>1.047042456665208</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.51277492742985</v>
+        <v>28.76064577285822</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1609713260960539</v>
+        <v>0.161016326096054</v>
       </c>
       <c r="C8">
-        <v>6748.024367298106</v>
+        <v>6681.509508153338</v>
       </c>
       <c r="D8">
-        <v>6951.024367298106</v>
+        <v>6948.309508153338</v>
       </c>
       <c r="E8">
-        <v>-1117</v>
+        <v>-1053.2</v>
       </c>
       <c r="F8">
-        <v>382.8</v>
+        <v>446.6</v>
       </c>
       <c r="G8">
         <v>179.8</v>
@@ -1937,28 +1937,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M8">
-        <v>19.25484</v>
+        <v>22.46398</v>
       </c>
       <c r="N8">
-        <v>534.5267926530613</v>
+        <v>531.3176526530613</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>534.5267926530613</v>
+        <v>531.3176526530613</v>
       </c>
       <c r="Q8">
-        <v>894.8267926530613</v>
+        <v>891.6176526530612</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1680354532936744</v>
+        <v>0.1693498130065096</v>
       </c>
       <c r="T8">
-        <v>1.047042456665208</v>
+        <v>1.058300977704619</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.76064577285822</v>
+        <v>24.65198209102133</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1610163260960539</v>
+        <v>0.161061326096054</v>
       </c>
       <c r="C9">
-        <v>6681.509508153339</v>
+        <v>6614.996768863783</v>
       </c>
       <c r="D9">
-        <v>6948.309508153339</v>
+        <v>6945.596768863783</v>
       </c>
       <c r="E9">
-        <v>-1053.2</v>
+        <v>-989.3999999999999</v>
       </c>
       <c r="F9">
-        <v>446.6</v>
+        <v>510.4</v>
       </c>
       <c r="G9">
         <v>179.8</v>
@@ -2019,28 +2019,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M9">
-        <v>22.46398</v>
+        <v>25.67312</v>
       </c>
       <c r="N9">
-        <v>531.3176526530613</v>
+        <v>528.1085126530612</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>531.3176526530613</v>
+        <v>528.1085126530612</v>
       </c>
       <c r="Q9">
-        <v>891.6176526530612</v>
+        <v>888.4085126530612</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1693498130065096</v>
+        <v>0.1706927457565804</v>
       </c>
       <c r="T9">
-        <v>1.058300977704619</v>
+        <v>1.069804249201409</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.65198209102133</v>
+        <v>21.57048432964366</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.161061326096054</v>
+        <v>0.161106326096054</v>
       </c>
       <c r="C10">
-        <v>6614.996768863783</v>
+        <v>6548.486146947528</v>
       </c>
       <c r="D10">
-        <v>6945.596768863783</v>
+        <v>6942.886146947528</v>
       </c>
       <c r="E10">
-        <v>-989.3999999999999</v>
+        <v>-925.6</v>
       </c>
       <c r="F10">
-        <v>510.4</v>
+        <v>574.1999999999999</v>
       </c>
       <c r="G10">
         <v>179.8</v>
@@ -2101,28 +2101,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M10">
-        <v>25.67312</v>
+        <v>28.88226</v>
       </c>
       <c r="N10">
-        <v>528.1085126530612</v>
+        <v>524.8993726530613</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>528.1085126530612</v>
+        <v>524.8993726530613</v>
       </c>
       <c r="Q10">
-        <v>888.4085126530612</v>
+        <v>885.1993726530612</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1706927457565804</v>
+        <v>0.1720651935121472</v>
       </c>
       <c r="T10">
-        <v>1.069804249201409</v>
+        <v>1.081560339851974</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.57048432964366</v>
+        <v>19.17376384857215</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.161106326096054</v>
+        <v>0.161151326096054</v>
       </c>
       <c r="C11">
-        <v>6548.486146947528</v>
+        <v>6481.977639926528</v>
       </c>
       <c r="D11">
-        <v>6942.886146947528</v>
+        <v>6940.177639926528</v>
       </c>
       <c r="E11">
-        <v>-925.6</v>
+        <v>-861.8</v>
       </c>
       <c r="F11">
-        <v>574.1999999999999</v>
+        <v>638</v>
       </c>
       <c r="G11">
         <v>179.8</v>
@@ -2183,28 +2183,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M11">
-        <v>28.88226</v>
+        <v>32.0914</v>
       </c>
       <c r="N11">
-        <v>524.8993726530613</v>
+        <v>521.6902326530612</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>524.8993726530613</v>
+        <v>521.6902326530612</v>
       </c>
       <c r="Q11">
-        <v>885.1993726530612</v>
+        <v>881.9902326530612</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1720651935121472</v>
+        <v>0.1734681401067266</v>
       </c>
       <c r="T11">
-        <v>1.081560339851974</v>
+        <v>1.09357767696144</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.17376384857215</v>
+        <v>17.25638746371493</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.161151326096054</v>
+        <v>0.161196326096054</v>
       </c>
       <c r="C12">
-        <v>6481.977639926528</v>
+        <v>6415.471245326612</v>
       </c>
       <c r="D12">
-        <v>6940.177639926528</v>
+        <v>6937.471245326612</v>
       </c>
       <c r="E12">
-        <v>-861.8</v>
+        <v>-798</v>
       </c>
       <c r="F12">
-        <v>638</v>
+        <v>701.8</v>
       </c>
       <c r="G12">
         <v>179.8</v>
@@ -2265,28 +2265,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M12">
-        <v>32.0914</v>
+        <v>35.30054</v>
       </c>
       <c r="N12">
-        <v>521.6902326530612</v>
+        <v>518.4810926530613</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>521.6902326530612</v>
+        <v>518.4810926530613</v>
       </c>
       <c r="Q12">
-        <v>881.9902326530612</v>
+        <v>878.7810926530613</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1734681401067266</v>
+        <v>0.1749026135910719</v>
       </c>
       <c r="T12">
-        <v>1.09357767696144</v>
+        <v>1.10586506659022</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.25638746371493</v>
+        <v>15.68762496701357</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.161196326096054</v>
+        <v>0.161241326096054</v>
       </c>
       <c r="C13">
-        <v>6415.471245326612</v>
+        <v>6348.966960677457</v>
       </c>
       <c r="D13">
-        <v>6937.471245326612</v>
+        <v>6934.766960677457</v>
       </c>
       <c r="E13">
-        <v>-798</v>
+        <v>-734.1999999999999</v>
       </c>
       <c r="F13">
-        <v>701.8</v>
+        <v>765.6</v>
       </c>
       <c r="G13">
         <v>179.8</v>
@@ -2347,28 +2347,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M13">
-        <v>35.30054</v>
+        <v>38.50968</v>
       </c>
       <c r="N13">
-        <v>518.4810926530613</v>
+        <v>515.2719526530612</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>518.4810926530613</v>
+        <v>515.2719526530612</v>
       </c>
       <c r="Q13">
-        <v>878.7810926530613</v>
+        <v>875.5719526530612</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1749026135910719</v>
+        <v>0.1763696887455158</v>
       </c>
       <c r="T13">
-        <v>1.10586506659022</v>
+        <v>1.1184317150742</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.68762496701357</v>
+        <v>14.38032288642911</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.161241326096054</v>
+        <v>0.161286326096054</v>
       </c>
       <c r="C14">
-        <v>6348.966960677457</v>
+        <v>6282.464783512596</v>
       </c>
       <c r="D14">
-        <v>6934.766960677457</v>
+        <v>6932.064783512596</v>
       </c>
       <c r="E14">
-        <v>-734.1999999999999</v>
+        <v>-670.4</v>
       </c>
       <c r="F14">
-        <v>765.6</v>
+        <v>829.4</v>
       </c>
       <c r="G14">
         <v>179.8</v>
@@ -2429,28 +2429,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M14">
-        <v>38.50968</v>
+        <v>41.71881999999999</v>
       </c>
       <c r="N14">
-        <v>515.2719526530612</v>
+        <v>512.0628126530612</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>515.2719526530612</v>
+        <v>512.0628126530612</v>
       </c>
       <c r="Q14">
-        <v>875.5719526530612</v>
+        <v>872.3628126530612</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1763696887455158</v>
+        <v>0.1778704897655793</v>
       </c>
       <c r="T14">
-        <v>1.1184317150742</v>
+        <v>1.131287252029076</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.38032288642911</v>
+        <v>13.27414420285764</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.161286326096054</v>
+        <v>0.161541326096054</v>
       </c>
       <c r="C15">
-        <v>6282.464783512596</v>
+        <v>6203.392135622518</v>
       </c>
       <c r="D15">
-        <v>6932.064783512596</v>
+        <v>6916.792135622518</v>
       </c>
       <c r="E15">
-        <v>-670.4</v>
+        <v>-606.5999999999999</v>
       </c>
       <c r="F15">
-        <v>829.4</v>
+        <v>893.2</v>
       </c>
       <c r="G15">
         <v>179.8</v>
@@ -2511,45 +2511,45 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M15">
-        <v>41.71881999999999</v>
+        <v>46.26776</v>
       </c>
       <c r="N15">
-        <v>512.0628126530612</v>
+        <v>507.5138726530612</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>512.0628126530612</v>
+        <v>507.5138726530612</v>
       </c>
       <c r="Q15">
-        <v>872.3628126530612</v>
+        <v>867.8138726530613</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1778704897655793</v>
+        <v>0.1794061931349465</v>
       </c>
       <c r="T15">
-        <v>1.131287252029076</v>
+        <v>1.144441754959646</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.27414420285764</v>
+        <v>11.96906080288004</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.161541326096054</v>
+        <v>0.161601326096054</v>
       </c>
       <c r="C16">
-        <v>6203.392135622518</v>
+        <v>6136.008346540577</v>
       </c>
       <c r="D16">
-        <v>6916.792135622518</v>
+        <v>6913.208346540577</v>
       </c>
       <c r="E16">
-        <v>-606.5999999999999</v>
+        <v>-542.7999999999998</v>
       </c>
       <c r="F16">
-        <v>893.2</v>
+        <v>957.0000000000001</v>
       </c>
       <c r="G16">
         <v>179.8</v>
@@ -2593,28 +2593,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M16">
-        <v>46.26776</v>
+        <v>49.5726</v>
       </c>
       <c r="N16">
-        <v>507.5138726530612</v>
+        <v>504.2090326530612</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>507.5138726530612</v>
+        <v>504.2090326530612</v>
       </c>
       <c r="Q16">
-        <v>867.8138726530613</v>
+        <v>864.5090326530612</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1794061931349465</v>
+        <v>0.18097803070124</v>
       </c>
       <c r="T16">
-        <v>1.144441754959646</v>
+        <v>1.157905775606231</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.96906080288004</v>
+        <v>11.17112341602138</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.161601326096054</v>
+        <v>0.1616613260960539</v>
       </c>
       <c r="C17">
-        <v>6136.008346540577</v>
+        <v>6068.628269263985</v>
       </c>
       <c r="D17">
-        <v>6913.208346540577</v>
+        <v>6909.628269263985</v>
       </c>
       <c r="E17">
-        <v>-542.8</v>
+        <v>-478.9999999999999</v>
       </c>
       <c r="F17">
-        <v>957</v>
+        <v>1020.8</v>
       </c>
       <c r="G17">
         <v>179.8</v>
@@ -2675,28 +2675,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M17">
-        <v>49.5726</v>
+        <v>52.87744</v>
       </c>
       <c r="N17">
-        <v>504.2090326530612</v>
+        <v>500.9041926530613</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>504.2090326530612</v>
+        <v>500.9041926530613</v>
       </c>
       <c r="Q17">
-        <v>864.5090326530612</v>
+        <v>861.2041926530612</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.18097803070124</v>
+        <v>0.1825872929714928</v>
       </c>
       <c r="T17">
-        <v>1.157905775606231</v>
+        <v>1.171690368172971</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.17112341602138</v>
+        <v>10.47292820252004</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1616613260960539</v>
+        <v>0.161721326096054</v>
       </c>
       <c r="C18">
-        <v>6068.628269263985</v>
+        <v>6001.251898029131</v>
       </c>
       <c r="D18">
-        <v>6909.628269263985</v>
+        <v>6906.051898029131</v>
       </c>
       <c r="E18">
-        <v>-478.9999999999999</v>
+        <v>-415.1999999999998</v>
       </c>
       <c r="F18">
-        <v>1020.8</v>
+        <v>1084.6</v>
       </c>
       <c r="G18">
         <v>179.8</v>
@@ -2757,28 +2757,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M18">
-        <v>52.87744</v>
+        <v>56.18228000000001</v>
       </c>
       <c r="N18">
-        <v>500.9041926530613</v>
+        <v>497.5993526530613</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>500.9041926530613</v>
+        <v>497.5993526530613</v>
       </c>
       <c r="Q18">
-        <v>861.2041926530612</v>
+        <v>857.8993526530612</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1825872929714928</v>
+        <v>0.1842353326458482</v>
       </c>
       <c r="T18">
-        <v>1.171690368172971</v>
+        <v>1.185807119596742</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.47292820252004</v>
+        <v>9.856873602371801</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.161721326096054</v>
+        <v>0.1620873260960539</v>
       </c>
       <c r="C19">
-        <v>6001.251898029131</v>
+        <v>5915.715952423237</v>
       </c>
       <c r="D19">
-        <v>6906.051898029131</v>
+        <v>6884.315952423238</v>
       </c>
       <c r="E19">
-        <v>-415.1999999999998</v>
+        <v>-351.3999999999999</v>
       </c>
       <c r="F19">
-        <v>1084.6</v>
+        <v>1148.4</v>
       </c>
       <c r="G19">
         <v>179.8</v>
@@ -2839,45 +2839,45 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M19">
-        <v>56.18228000000001</v>
+        <v>61.43940000000001</v>
       </c>
       <c r="N19">
-        <v>497.5993526530613</v>
+        <v>492.3422326530613</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>497.5993526530613</v>
+        <v>492.3422326530613</v>
       </c>
       <c r="Q19">
-        <v>857.8993526530612</v>
+        <v>852.6422326530612</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1842353326458482</v>
+        <v>0.1859235684098219</v>
       </c>
       <c r="T19">
-        <v>1.185807119596742</v>
+        <v>1.200268182030849</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.856873602371801</v>
+        <v>9.013460949375503</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.162087326096054</v>
+        <v>0.162164326096054</v>
       </c>
       <c r="C20">
-        <v>5915.715952423237</v>
+        <v>5847.360498478537</v>
       </c>
       <c r="D20">
-        <v>6884.315952423237</v>
+        <v>6879.760498478537</v>
       </c>
       <c r="E20">
-        <v>-351.4000000000001</v>
+        <v>-287.5999999999999</v>
       </c>
       <c r="F20">
-        <v>1148.4</v>
+        <v>1212.2</v>
       </c>
       <c r="G20">
         <v>179.8</v>
@@ -2921,28 +2921,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M20">
-        <v>61.43939999999999</v>
+        <v>64.8527</v>
       </c>
       <c r="N20">
-        <v>492.3422326530613</v>
+        <v>488.9289326530612</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>492.3422326530613</v>
+        <v>488.9289326530612</v>
       </c>
       <c r="Q20">
-        <v>852.6422326530612</v>
+        <v>849.2289326530612</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1859235684098219</v>
+        <v>0.187653489007474</v>
       </c>
       <c r="T20">
-        <v>1.200268182030849</v>
+        <v>1.215086307734933</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.013460949375505</v>
+        <v>8.539068267829423</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.162164326096054</v>
+        <v>0.162241326096054</v>
       </c>
       <c r="C21">
-        <v>5847.360498478537</v>
+        <v>5779.01106936996</v>
       </c>
       <c r="D21">
-        <v>6879.760498478537</v>
+        <v>6875.21106936996</v>
       </c>
       <c r="E21">
-        <v>-287.5999999999999</v>
+        <v>-223.8</v>
       </c>
       <c r="F21">
-        <v>1212.2</v>
+        <v>1276</v>
       </c>
       <c r="G21">
         <v>179.8</v>
@@ -3003,28 +3003,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M21">
-        <v>64.8527</v>
+        <v>68.26600000000001</v>
       </c>
       <c r="N21">
-        <v>488.9289326530612</v>
+        <v>485.5156326530612</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>488.9289326530612</v>
+        <v>485.5156326530612</v>
       </c>
       <c r="Q21">
-        <v>849.2289326530612</v>
+        <v>845.8156326530611</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.187653489007474</v>
+        <v>0.1894266576200674</v>
       </c>
       <c r="T21">
-        <v>1.215086307734933</v>
+        <v>1.23027488658162</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.539068267829423</v>
+        <v>8.112114854437952</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.162241326096054</v>
+        <v>0.162318326096054</v>
       </c>
       <c r="C22">
-        <v>5779.01106936996</v>
+        <v>5710.667653153138</v>
       </c>
       <c r="D22">
-        <v>6875.21106936996</v>
+        <v>6870.667653153138</v>
       </c>
       <c r="E22">
-        <v>-223.8</v>
+        <v>-159.9999999999998</v>
       </c>
       <c r="F22">
-        <v>1276</v>
+        <v>1339.8</v>
       </c>
       <c r="G22">
         <v>179.8</v>
@@ -3085,28 +3085,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M22">
-        <v>68.26600000000001</v>
+        <v>71.67930000000001</v>
       </c>
       <c r="N22">
-        <v>485.5156326530612</v>
+        <v>482.1023326530612</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>485.5156326530612</v>
+        <v>482.1023326530612</v>
       </c>
       <c r="Q22">
-        <v>845.8156326530611</v>
+        <v>842.4023326530612</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1894266576200674</v>
+        <v>0.1912447165772835</v>
       </c>
       <c r="T22">
-        <v>1.23027488658162</v>
+        <v>1.245847986411767</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.112114854437952</v>
+        <v>7.725823670893287</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.162318326096054</v>
+        <v>0.162571326096054</v>
       </c>
       <c r="C23">
-        <v>5710.667653153138</v>
+        <v>5631.98147369143</v>
       </c>
       <c r="D23">
-        <v>6870.667653153138</v>
+        <v>6855.78147369143</v>
       </c>
       <c r="E23">
-        <v>-160</v>
+        <v>-96.20000000000005</v>
       </c>
       <c r="F23">
-        <v>1339.8</v>
+        <v>1403.6</v>
       </c>
       <c r="G23">
         <v>179.8</v>
@@ -3167,45 +3167,45 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M23">
-        <v>71.6793</v>
+        <v>76.21548</v>
       </c>
       <c r="N23">
-        <v>482.1023326530612</v>
+        <v>477.5661526530612</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>482.1023326530612</v>
+        <v>477.5661526530612</v>
       </c>
       <c r="Q23">
-        <v>842.4023326530612</v>
+        <v>837.8661526530611</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1912447165772835</v>
+        <v>0.1931093924308384</v>
       </c>
       <c r="T23">
-        <v>1.245847986411767</v>
+        <v>1.261820396493969</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.725823670893288</v>
+        <v>7.26599940921531</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.162571326096054</v>
+        <v>0.162656326096054</v>
       </c>
       <c r="C24">
-        <v>5631.98147369143</v>
+        <v>5563.194654023791</v>
       </c>
       <c r="D24">
-        <v>6855.78147369143</v>
+        <v>6850.794654023791</v>
       </c>
       <c r="E24">
-        <v>-96.20000000000005</v>
+        <v>-32.39999999999986</v>
       </c>
       <c r="F24">
-        <v>1403.6</v>
+        <v>1467.4</v>
       </c>
       <c r="G24">
         <v>179.8</v>
@@ -3249,28 +3249,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M24">
-        <v>76.21548</v>
+        <v>79.67982000000001</v>
       </c>
       <c r="N24">
-        <v>477.5661526530612</v>
+        <v>474.1018126530612</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>477.5661526530612</v>
+        <v>474.1018126530612</v>
       </c>
       <c r="Q24">
-        <v>837.8661526530611</v>
+        <v>834.4018126530611</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1931093924308384</v>
+        <v>0.1950225014234467</v>
       </c>
       <c r="T24">
-        <v>1.261820396493969</v>
+        <v>1.278207674370514</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.26599940921531</v>
+        <v>6.950086391423339</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.162656326096054</v>
+        <v>0.162741326096054</v>
       </c>
       <c r="C25">
-        <v>5563.194654023791</v>
+        <v>5494.415083798003</v>
       </c>
       <c r="D25">
-        <v>6850.794654023791</v>
+        <v>6845.815083798003</v>
       </c>
       <c r="E25">
-        <v>-32.39999999999986</v>
+        <v>31.40000000000009</v>
       </c>
       <c r="F25">
-        <v>1467.4</v>
+        <v>1531.2</v>
       </c>
       <c r="G25">
         <v>179.8</v>
@@ -3331,28 +3331,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M25">
-        <v>79.67982000000001</v>
+        <v>83.14416</v>
       </c>
       <c r="N25">
-        <v>474.1018126530612</v>
+        <v>470.6374726530613</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>474.1018126530612</v>
+        <v>470.6374726530613</v>
       </c>
       <c r="Q25">
-        <v>834.4018126530611</v>
+        <v>830.9374726530611</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1950225014234467</v>
+        <v>0.1969859553895447</v>
       </c>
       <c r="T25">
-        <v>1.278207674370514</v>
+        <v>1.295026196401705</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.950086391423339</v>
+        <v>6.660499458447367</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1627413260960539</v>
+        <v>0.162826326096054</v>
       </c>
       <c r="C26">
-        <v>5494.415083798005</v>
+        <v>5425.642747217556</v>
       </c>
       <c r="D26">
-        <v>6845.815083798005</v>
+        <v>6840.842747217555</v>
       </c>
       <c r="E26">
-        <v>31.40000000000009</v>
+        <v>95.20000000000005</v>
       </c>
       <c r="F26">
-        <v>1531.2</v>
+        <v>1595</v>
       </c>
       <c r="G26">
         <v>179.8</v>
@@ -3413,28 +3413,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M26">
-        <v>83.14416</v>
+        <v>86.60850000000001</v>
       </c>
       <c r="N26">
-        <v>470.6374726530613</v>
+        <v>467.1731326530613</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>470.6374726530613</v>
+        <v>467.1731326530613</v>
       </c>
       <c r="Q26">
-        <v>830.9374726530611</v>
+        <v>827.4731326530612</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1969859553895447</v>
+        <v>0.1990017681280719</v>
       </c>
       <c r="T26">
-        <v>1.295026196401705</v>
+        <v>1.312293212353728</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.660499458447367</v>
+        <v>6.394079480109472</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.162826326096054</v>
+        <v>0.1629113260960539</v>
       </c>
       <c r="C27">
-        <v>5425.642747217556</v>
+        <v>5356.877628531798</v>
       </c>
       <c r="D27">
-        <v>6840.842747217555</v>
+        <v>6835.877628531798</v>
       </c>
       <c r="E27">
-        <v>95.20000000000005</v>
+        <v>159</v>
       </c>
       <c r="F27">
-        <v>1595</v>
+        <v>1658.8</v>
       </c>
       <c r="G27">
         <v>179.8</v>
@@ -3495,28 +3495,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M27">
-        <v>86.60850000000001</v>
+        <v>90.07284</v>
       </c>
       <c r="N27">
-        <v>467.1731326530613</v>
+        <v>463.7087926530613</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>467.1731326530613</v>
+        <v>463.7087926530613</v>
       </c>
       <c r="Q27">
-        <v>827.4731326530612</v>
+        <v>824.0087926530612</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1990017681280719</v>
+        <v>0.2010720622919648</v>
       </c>
       <c r="T27">
-        <v>1.312293212353728</v>
+        <v>1.330026904412562</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.394079480109472</v>
+        <v>6.148153346259108</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1629113260960539</v>
+        <v>0.163266326096054</v>
       </c>
       <c r="C28">
-        <v>5356.877628531798</v>
+        <v>5272.418630853223</v>
       </c>
       <c r="D28">
-        <v>6835.877628531798</v>
+        <v>6815.218630853223</v>
       </c>
       <c r="E28">
-        <v>159</v>
+        <v>222.8000000000002</v>
       </c>
       <c r="F28">
-        <v>1658.8</v>
+        <v>1722.6</v>
       </c>
       <c r="G28">
         <v>179.8</v>
@@ -3577,45 +3577,45 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M28">
-        <v>90.07284</v>
+        <v>95.25978000000001</v>
       </c>
       <c r="N28">
-        <v>463.7087926530613</v>
+        <v>458.5218526530613</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>463.7087926530613</v>
+        <v>458.5218526530613</v>
       </c>
       <c r="Q28">
-        <v>824.0087926530612</v>
+        <v>818.8218526530612</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2010720622919648</v>
+        <v>0.2031990768439096</v>
       </c>
       <c r="T28">
-        <v>1.330026904412562</v>
+        <v>1.348246451048351</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.148153346259108</v>
+        <v>5.813383493569492</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.163266326096054</v>
+        <v>0.1633613260960539</v>
       </c>
       <c r="C29">
-        <v>5272.418630853223</v>
+        <v>5203.111328482359</v>
       </c>
       <c r="D29">
-        <v>6815.218630853223</v>
+        <v>6809.711328482359</v>
       </c>
       <c r="E29">
-        <v>222.8000000000002</v>
+        <v>286.6000000000001</v>
       </c>
       <c r="F29">
-        <v>1722.6</v>
+        <v>1786.4</v>
       </c>
       <c r="G29">
         <v>179.8</v>
@@ -3659,28 +3659,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M29">
-        <v>95.25978000000001</v>
+        <v>98.78792000000001</v>
       </c>
       <c r="N29">
-        <v>458.5218526530613</v>
+        <v>454.9937126530613</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>458.5218526530613</v>
+        <v>454.9937126530613</v>
       </c>
       <c r="Q29">
-        <v>818.8218526530612</v>
+        <v>815.2937126530612</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2031990768439096</v>
+        <v>0.2053851751334083</v>
       </c>
       <c r="T29">
-        <v>1.348246451048351</v>
+        <v>1.3669720962018</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.813383493569492</v>
+        <v>5.605762654513438</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1633613260960539</v>
+        <v>0.163456326096054</v>
       </c>
       <c r="C30">
-        <v>5203.111328482359</v>
+        <v>5133.812919704254</v>
       </c>
       <c r="D30">
-        <v>6809.711328482359</v>
+        <v>6804.212919704255</v>
       </c>
       <c r="E30">
-        <v>286.6000000000001</v>
+        <v>350.4000000000003</v>
       </c>
       <c r="F30">
-        <v>1786.4</v>
+        <v>1850.2</v>
       </c>
       <c r="G30">
         <v>179.8</v>
@@ -3741,28 +3741,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M30">
-        <v>98.78792000000001</v>
+        <v>102.31606</v>
       </c>
       <c r="N30">
-        <v>454.9937126530613</v>
+        <v>451.4655726530613</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>454.9937126530613</v>
+        <v>451.4655726530613</v>
       </c>
       <c r="Q30">
-        <v>815.2937126530612</v>
+        <v>811.7655726530612</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2053851751334083</v>
+        <v>0.207632853656414</v>
       </c>
       <c r="T30">
-        <v>1.3669720962018</v>
+        <v>1.386225224317318</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.605762654513438</v>
+        <v>5.412460494012975</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1634563260960539</v>
+        <v>0.1635513260960539</v>
       </c>
       <c r="C31">
-        <v>5133.812919704258</v>
+        <v>5064.523382993268</v>
       </c>
       <c r="D31">
-        <v>6804.212919704258</v>
+        <v>6798.723382993267</v>
       </c>
       <c r="E31">
-        <v>350.3999999999999</v>
+        <v>414.2</v>
       </c>
       <c r="F31">
-        <v>1850.2</v>
+        <v>1914</v>
       </c>
       <c r="G31">
         <v>179.8</v>
@@ -3823,28 +3823,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M31">
-        <v>102.31606</v>
+        <v>105.8442</v>
       </c>
       <c r="N31">
-        <v>451.4655726530613</v>
+        <v>447.9374326530613</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>451.4655726530613</v>
+        <v>447.9374326530613</v>
       </c>
       <c r="Q31">
-        <v>811.7655726530612</v>
+        <v>808.2374326530612</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.207632853656414</v>
+        <v>0.2099447515657914</v>
       </c>
       <c r="T31">
-        <v>1.386225224317318</v>
+        <v>1.406028441807566</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.412460494012976</v>
+        <v>5.232045144212543</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1635513260960539</v>
+        <v>0.163646326096054</v>
       </c>
       <c r="C32">
-        <v>5064.523382993268</v>
+        <v>4995.24269689315</v>
       </c>
       <c r="D32">
-        <v>6798.723382993267</v>
+        <v>6793.24269689315</v>
       </c>
       <c r="E32">
-        <v>414.2</v>
+        <v>478</v>
       </c>
       <c r="F32">
-        <v>1914</v>
+        <v>1977.8</v>
       </c>
       <c r="G32">
         <v>179.8</v>
@@ -3905,28 +3905,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M32">
-        <v>105.8442</v>
+        <v>109.37234</v>
       </c>
       <c r="N32">
-        <v>447.9374326530613</v>
+        <v>444.4092926530612</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>447.9374326530613</v>
+        <v>444.4092926530612</v>
       </c>
       <c r="Q32">
-        <v>808.2374326530612</v>
+        <v>804.7092926530612</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2099447515657914</v>
+        <v>0.2123236610087739</v>
       </c>
       <c r="T32">
-        <v>1.406028441807566</v>
+        <v>1.426405665601878</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.232045144212543</v>
+        <v>5.063269494399234</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.163646326096054</v>
+        <v>0.1637413260960539</v>
       </c>
       <c r="C33">
-        <v>4995.24269689315</v>
+        <v>4925.9708400168</v>
       </c>
       <c r="D33">
-        <v>6793.24269689315</v>
+        <v>6787.7708400168</v>
       </c>
       <c r="E33">
-        <v>478</v>
+        <v>541.8000000000002</v>
       </c>
       <c r="F33">
-        <v>1977.8</v>
+        <v>2041.6</v>
       </c>
       <c r="G33">
         <v>179.8</v>
@@ -3987,28 +3987,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M33">
-        <v>109.37234</v>
+        <v>112.90048</v>
       </c>
       <c r="N33">
-        <v>444.4092926530612</v>
+        <v>440.8811526530612</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>444.4092926530612</v>
+        <v>440.8811526530612</v>
       </c>
       <c r="Q33">
-        <v>804.7092926530612</v>
+        <v>801.1811526530612</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2123236610087739</v>
+        <v>0.2147725383765499</v>
       </c>
       <c r="T33">
-        <v>1.426405665601878</v>
+        <v>1.447382219507788</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.063269494399234</v>
+        <v>4.905042322699258</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1637413260960539</v>
+        <v>0.163836326096054</v>
       </c>
       <c r="C34">
-        <v>4925.9708400168</v>
+        <v>4856.70779104595</v>
       </c>
       <c r="D34">
-        <v>6787.7708400168</v>
+        <v>6782.30779104595</v>
       </c>
       <c r="E34">
-        <v>541.8000000000002</v>
+        <v>605.6000000000001</v>
       </c>
       <c r="F34">
-        <v>2041.6</v>
+        <v>2105.4</v>
       </c>
       <c r="G34">
         <v>179.8</v>
@@ -4069,28 +4069,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M34">
-        <v>112.90048</v>
+        <v>116.42862</v>
       </c>
       <c r="N34">
-        <v>440.8811526530612</v>
+        <v>437.3530126530612</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>440.8811526530612</v>
+        <v>437.3530126530612</v>
       </c>
       <c r="Q34">
-        <v>801.1811526530612</v>
+        <v>797.6530126530612</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2147725383765499</v>
+        <v>0.2172945165612746</v>
       </c>
       <c r="T34">
-        <v>1.447382219507788</v>
+        <v>1.468984939201934</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.905042322699258</v>
+        <v>4.756404676556857</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.163836326096054</v>
+        <v>0.163931326096054</v>
       </c>
       <c r="C35">
-        <v>4856.70779104595</v>
+        <v>4787.453528730928</v>
       </c>
       <c r="D35">
-        <v>6782.30779104595</v>
+        <v>6776.853528730929</v>
       </c>
       <c r="E35">
-        <v>605.6000000000001</v>
+        <v>669.4000000000003</v>
       </c>
       <c r="F35">
-        <v>2105.4</v>
+        <v>2169.2</v>
       </c>
       <c r="G35">
         <v>179.8</v>
@@ -4151,28 +4151,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M35">
-        <v>116.42862</v>
+        <v>119.95676</v>
       </c>
       <c r="N35">
-        <v>437.3530126530612</v>
+        <v>433.8248726530612</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>437.3530126530612</v>
+        <v>433.8248726530612</v>
       </c>
       <c r="Q35">
-        <v>797.6530126530612</v>
+        <v>794.1248726530612</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2172945165612746</v>
+        <v>0.2198929183273545</v>
       </c>
       <c r="T35">
-        <v>1.468984939201934</v>
+        <v>1.4912422867656</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.756404676556857</v>
+        <v>4.616510421364008</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.163931326096054</v>
+        <v>0.1649013260960539</v>
       </c>
       <c r="C36">
-        <v>4787.453528730928</v>
+        <v>4668.460625861255</v>
       </c>
       <c r="D36">
-        <v>6776.853528730929</v>
+        <v>6721.660625861255</v>
       </c>
       <c r="E36">
-        <v>669.4000000000003</v>
+        <v>733.2</v>
       </c>
       <c r="F36">
-        <v>2169.2</v>
+        <v>2233</v>
       </c>
       <c r="G36">
         <v>179.8</v>
@@ -4233,45 +4233,45 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M36">
-        <v>119.95676</v>
+        <v>129.0674</v>
       </c>
       <c r="N36">
-        <v>433.8248726530612</v>
+        <v>424.7142326530612</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>433.8248726530612</v>
+        <v>424.7142326530612</v>
       </c>
       <c r="Q36">
-        <v>794.1248726530612</v>
+        <v>785.0142326530612</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2198929183273545</v>
+        <v>0.2225712709170061</v>
       </c>
       <c r="T36">
-        <v>1.4912422867656</v>
+        <v>1.514184475792763</v>
       </c>
       <c r="U36">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0</v>
       </c>
       <c r="W36">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.616510421364008</v>
+        <v>4.29063909750302</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1649013260960539</v>
+        <v>0.1650213260960539</v>
       </c>
       <c r="C37">
-        <v>4668.460625861255</v>
+        <v>4597.89506384718</v>
       </c>
       <c r="D37">
-        <v>6721.660625861255</v>
+        <v>6714.89506384718</v>
       </c>
       <c r="E37">
-        <v>733.2</v>
+        <v>797.0000000000002</v>
       </c>
       <c r="F37">
-        <v>2233</v>
+        <v>2296.8</v>
       </c>
       <c r="G37">
         <v>179.8</v>
@@ -4315,28 +4315,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M37">
-        <v>129.0674</v>
+        <v>132.75504</v>
       </c>
       <c r="N37">
-        <v>424.7142326530612</v>
+        <v>421.0265926530612</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>424.7142326530612</v>
+        <v>421.0265926530612</v>
       </c>
       <c r="Q37">
-        <v>785.0142326530612</v>
+        <v>781.3265926530612</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2225712709170061</v>
+        <v>0.2253333220250843</v>
       </c>
       <c r="T37">
-        <v>1.514184475792763</v>
+        <v>1.537843608227025</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.29063909750302</v>
+        <v>4.171454678127936</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1650213260960539</v>
+        <v>0.165141326096054</v>
       </c>
       <c r="C38">
-        <v>4597.895063847178</v>
+        <v>4527.343107638702</v>
       </c>
       <c r="D38">
-        <v>6714.895063847178</v>
+        <v>6708.143107638703</v>
       </c>
       <c r="E38">
-        <v>796.9999999999998</v>
+        <v>860.8</v>
       </c>
       <c r="F38">
-        <v>2296.8</v>
+        <v>2360.6</v>
       </c>
       <c r="G38">
         <v>179.8</v>
@@ -4397,28 +4397,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M38">
-        <v>132.75504</v>
+        <v>136.44268</v>
       </c>
       <c r="N38">
-        <v>421.0265926530612</v>
+        <v>417.3389526530613</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>421.0265926530612</v>
+        <v>417.3389526530613</v>
       </c>
       <c r="Q38">
-        <v>781.3265926530612</v>
+        <v>777.6389526530612</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2253333220250843</v>
+        <v>0.2281830572953238</v>
       </c>
       <c r="T38">
-        <v>1.537843608227025</v>
+        <v>1.562253824230629</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.171454678127937</v>
+        <v>4.058712659800154</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.165141326096054</v>
+        <v>0.166591326096054</v>
       </c>
       <c r="C39">
-        <v>4527.343107638702</v>
+        <v>4383.017395897272</v>
       </c>
       <c r="D39">
-        <v>6708.143107638703</v>
+        <v>6627.617395897272</v>
       </c>
       <c r="E39">
-        <v>860.8</v>
+        <v>924.6000000000001</v>
       </c>
       <c r="F39">
-        <v>2360.6</v>
+        <v>2424.4</v>
       </c>
       <c r="G39">
         <v>179.8</v>
@@ -4479,45 +4479,45 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M39">
-        <v>136.44268</v>
+        <v>148.61572</v>
       </c>
       <c r="N39">
-        <v>417.3389526530613</v>
+        <v>405.1659126530612</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>417.3389526530613</v>
+        <v>405.1659126530612</v>
       </c>
       <c r="Q39">
-        <v>777.6389526530612</v>
+        <v>765.4659126530612</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2281830572953238</v>
+        <v>0.2311247195097644</v>
       </c>
       <c r="T39">
-        <v>1.562253824230629</v>
+        <v>1.587451466556929</v>
       </c>
       <c r="U39">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V39">
         <v>0</v>
       </c>
       <c r="W39">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.058712659800154</v>
+        <v>3.726265516548728</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.166591326096054</v>
+        <v>0.166746326096054</v>
       </c>
       <c r="C40">
-        <v>4383.017395897272</v>
+        <v>4310.723705104645</v>
       </c>
       <c r="D40">
-        <v>6627.617395897272</v>
+        <v>6619.123705104645</v>
       </c>
       <c r="E40">
-        <v>924.6000000000001</v>
+        <v>988.4000000000003</v>
       </c>
       <c r="F40">
-        <v>2424.4</v>
+        <v>2488.2</v>
       </c>
       <c r="G40">
         <v>179.8</v>
@@ -4561,28 +4561,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M40">
-        <v>148.61572</v>
+        <v>152.52666</v>
       </c>
       <c r="N40">
-        <v>405.1659126530612</v>
+        <v>401.2549726530613</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>405.1659126530612</v>
+        <v>401.2549726530613</v>
       </c>
       <c r="Q40">
-        <v>765.4659126530612</v>
+        <v>761.5549726530612</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2311247195097644</v>
+        <v>0.2341628296656622</v>
       </c>
       <c r="T40">
-        <v>1.587451466556929</v>
+        <v>1.613475261090649</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.726265516548728</v>
+        <v>3.630720246893633</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.166746326096054</v>
+        <v>0.166901326096054</v>
       </c>
       <c r="C41">
-        <v>4310.723705104645</v>
+        <v>4238.451756800153</v>
       </c>
       <c r="D41">
-        <v>6619.123705104645</v>
+        <v>6610.651756800153</v>
       </c>
       <c r="E41">
-        <v>988.4000000000003</v>
+        <v>1052.2</v>
       </c>
       <c r="F41">
-        <v>2488.2</v>
+        <v>2552</v>
       </c>
       <c r="G41">
         <v>179.8</v>
@@ -4643,28 +4643,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M41">
-        <v>152.52666</v>
+        <v>156.4376</v>
       </c>
       <c r="N41">
-        <v>401.2549726530613</v>
+        <v>397.3440326530613</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>401.2549726530613</v>
+        <v>397.3440326530613</v>
       </c>
       <c r="Q41">
-        <v>761.5549726530612</v>
+        <v>757.6440326530612</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2341628296656622</v>
+        <v>0.2373022101600899</v>
       </c>
       <c r="T41">
-        <v>1.613475261090649</v>
+        <v>1.64036651544216</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.630720246893633</v>
+        <v>3.539952240721293</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.166901326096054</v>
+        <v>0.1682043260960539</v>
       </c>
       <c r="C42">
-        <v>4238.451756800153</v>
+        <v>4104.281047579051</v>
       </c>
       <c r="D42">
-        <v>6610.651756800153</v>
+        <v>6540.281047579051</v>
       </c>
       <c r="E42">
-        <v>1052.2</v>
+        <v>1116</v>
       </c>
       <c r="F42">
-        <v>2552</v>
+        <v>2615.8</v>
       </c>
       <c r="G42">
         <v>179.8</v>
@@ -4725,45 +4725,45 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M42">
-        <v>156.4376</v>
+        <v>167.67278</v>
       </c>
       <c r="N42">
-        <v>397.3440326530613</v>
+        <v>386.1088526530613</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>397.3440326530613</v>
+        <v>386.1088526530613</v>
       </c>
       <c r="Q42">
-        <v>757.6440326530612</v>
+        <v>746.4088526530612</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2373022101600899</v>
+        <v>0.2405480103322948</v>
       </c>
       <c r="T42">
-        <v>1.64036651544216</v>
+        <v>1.66816933773779</v>
       </c>
       <c r="U42">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0</v>
       </c>
       <c r="W42">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.539952240721293</v>
+        <v>3.302752138141094</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1682043260960539</v>
+        <v>0.1683873260960539</v>
       </c>
       <c r="C43">
-        <v>4104.281047579051</v>
+        <v>4030.717628555054</v>
       </c>
       <c r="D43">
-        <v>6540.281047579051</v>
+        <v>6530.517628555054</v>
       </c>
       <c r="E43">
-        <v>1116</v>
+        <v>1179.8</v>
       </c>
       <c r="F43">
-        <v>2615.8</v>
+        <v>2679.6</v>
       </c>
       <c r="G43">
         <v>179.8</v>
@@ -4807,28 +4807,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M43">
-        <v>167.67278</v>
+        <v>171.76236</v>
       </c>
       <c r="N43">
-        <v>386.1088526530613</v>
+        <v>382.0192726530612</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>386.1088526530613</v>
+        <v>382.0192726530612</v>
       </c>
       <c r="Q43">
-        <v>746.4088526530612</v>
+        <v>742.3192726530611</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2405480103322948</v>
+        <v>0.2439057346483689</v>
       </c>
       <c r="T43">
-        <v>1.66816933773779</v>
+        <v>1.696930878043614</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.302752138141094</v>
+        <v>3.224115182471067</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.168387326096054</v>
+        <v>0.168570326096054</v>
       </c>
       <c r="C44">
-        <v>4030.717628555053</v>
+        <v>3957.183316005533</v>
       </c>
       <c r="D44">
-        <v>6530.517628555052</v>
+        <v>6520.783316005532</v>
       </c>
       <c r="E44">
-        <v>1179.8</v>
+        <v>1243.6</v>
       </c>
       <c r="F44">
-        <v>2679.6</v>
+        <v>2743.4</v>
       </c>
       <c r="G44">
         <v>179.8</v>
@@ -4889,28 +4889,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M44">
-        <v>171.76236</v>
+        <v>175.85194</v>
       </c>
       <c r="N44">
-        <v>382.0192726530613</v>
+        <v>377.9296926530612</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>382.0192726530613</v>
+        <v>377.9296926530612</v>
       </c>
       <c r="Q44">
-        <v>742.3192726530613</v>
+        <v>738.2296926530612</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2439057346483689</v>
+        <v>0.2473812738527262</v>
       </c>
       <c r="T44">
-        <v>1.696930878043613</v>
+        <v>1.726701595202274</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.224115182471068</v>
+        <v>3.149135759622903</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.168570326096054</v>
+        <v>0.168753326096054</v>
       </c>
       <c r="C45">
-        <v>3957.183316005533</v>
+        <v>3883.677979966906</v>
       </c>
       <c r="D45">
-        <v>6520.783316005532</v>
+        <v>6511.077979966905</v>
       </c>
       <c r="E45">
-        <v>1243.6</v>
+        <v>1307.4</v>
       </c>
       <c r="F45">
-        <v>2743.4</v>
+        <v>2807.2</v>
       </c>
       <c r="G45">
         <v>179.8</v>
@@ -4971,28 +4971,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M45">
-        <v>175.85194</v>
+        <v>179.94152</v>
       </c>
       <c r="N45">
-        <v>377.9296926530612</v>
+        <v>373.8401126530613</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>377.9296926530612</v>
+        <v>373.8401126530613</v>
       </c>
       <c r="Q45">
-        <v>738.2296926530612</v>
+        <v>734.1401126530612</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2473812738527262</v>
+        <v>0.2509809394572392</v>
       </c>
       <c r="T45">
-        <v>1.726701595202274</v>
+        <v>1.757535552259457</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.149135759622903</v>
+        <v>3.077564492358747</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.168753326096054</v>
+        <v>0.1689363260960539</v>
       </c>
       <c r="C46">
-        <v>3883.677979966906</v>
+        <v>3810.20149124818</v>
       </c>
       <c r="D46">
-        <v>6511.077979966905</v>
+        <v>6501.40149124818</v>
       </c>
       <c r="E46">
-        <v>1307.4</v>
+        <v>1371.2</v>
       </c>
       <c r="F46">
-        <v>2807.2</v>
+        <v>2871</v>
       </c>
       <c r="G46">
         <v>179.8</v>
@@ -5053,28 +5053,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M46">
-        <v>179.94152</v>
+        <v>184.0311</v>
       </c>
       <c r="N46">
-        <v>373.8401126530613</v>
+        <v>369.7505326530612</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>373.8401126530613</v>
+        <v>369.7505326530612</v>
       </c>
       <c r="Q46">
-        <v>734.1401126530612</v>
+        <v>730.0505326530612</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2509809394572392</v>
+        <v>0.2547115019928253</v>
       </c>
       <c r="T46">
-        <v>1.757535552259457</v>
+        <v>1.78949074411872</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.077564492358747</v>
+        <v>3.00917417030633</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1689363260960539</v>
+        <v>0.1727073260960539</v>
       </c>
       <c r="C47">
-        <v>3810.20149124818</v>
+        <v>3553.214968628197</v>
       </c>
       <c r="D47">
-        <v>6501.40149124818</v>
+        <v>6308.214968628197</v>
       </c>
       <c r="E47">
-        <v>1371.2</v>
+        <v>1435</v>
       </c>
       <c r="F47">
-        <v>2871</v>
+        <v>2934.8</v>
       </c>
       <c r="G47">
         <v>179.8</v>
@@ -5135,45 +5135,45 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M47">
-        <v>184.0311</v>
+        <v>211.01212</v>
       </c>
       <c r="N47">
-        <v>369.7505326530612</v>
+        <v>342.7695126530612</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>369.7505326530612</v>
+        <v>342.7695126530612</v>
       </c>
       <c r="Q47">
-        <v>730.0505326530612</v>
+        <v>703.0695126530611</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2547115019928253</v>
+        <v>0.258580233511211</v>
       </c>
       <c r="T47">
-        <v>1.78949074411872</v>
+        <v>1.8226294616024</v>
       </c>
       <c r="U47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0</v>
       </c>
       <c r="W47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.00917417030633</v>
+        <v>2.624406752811455</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1727073260960539</v>
+        <v>0.1729683260960539</v>
       </c>
       <c r="C48">
-        <v>3553.214968628197</v>
+        <v>3476.468001742996</v>
       </c>
       <c r="D48">
-        <v>6308.214968628197</v>
+        <v>6295.268001742996</v>
       </c>
       <c r="E48">
-        <v>1435</v>
+        <v>1498.8</v>
       </c>
       <c r="F48">
-        <v>2934.8</v>
+        <v>2998.6</v>
       </c>
       <c r="G48">
         <v>179.8</v>
@@ -5217,28 +5217,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M48">
-        <v>211.01212</v>
+        <v>215.59934</v>
       </c>
       <c r="N48">
-        <v>342.7695126530612</v>
+        <v>338.1822926530612</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>342.7695126530612</v>
+        <v>338.1822926530612</v>
       </c>
       <c r="Q48">
-        <v>703.0695126530611</v>
+        <v>698.4822926530612</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.258580233511211</v>
+        <v>0.262594954898215</v>
       </c>
       <c r="T48">
-        <v>1.8226294616024</v>
+        <v>1.857018696726974</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.624406752811455</v>
+        <v>2.568568311262275</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1729683260960539</v>
+        <v>0.173229326096054</v>
       </c>
       <c r="C49">
-        <v>3476.468001742996</v>
+        <v>3399.774070661414</v>
       </c>
       <c r="D49">
-        <v>6295.268001742996</v>
+        <v>6282.374070661414</v>
       </c>
       <c r="E49">
-        <v>1498.8</v>
+        <v>1562.6</v>
       </c>
       <c r="F49">
-        <v>2998.6</v>
+        <v>3062.4</v>
       </c>
       <c r="G49">
         <v>179.8</v>
@@ -5299,28 +5299,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M49">
-        <v>215.59934</v>
+        <v>220.18656</v>
       </c>
       <c r="N49">
-        <v>338.1822926530612</v>
+        <v>333.5950726530613</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>338.1822926530612</v>
+        <v>333.5950726530613</v>
       </c>
       <c r="Q49">
-        <v>698.4822926530612</v>
+        <v>693.8950726530612</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.262594954898215</v>
+        <v>0.2667640886462576</v>
       </c>
       <c r="T49">
-        <v>1.857018696726974</v>
+        <v>1.892730594740954</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.568568311262275</v>
+        <v>2.515056471444312</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.173229326096054</v>
+        <v>0.175401326096054</v>
       </c>
       <c r="C50">
-        <v>3399.774070661414</v>
+        <v>3230.687212166129</v>
       </c>
       <c r="D50">
-        <v>6282.374070661414</v>
+        <v>6177.087212166129</v>
       </c>
       <c r="E50">
-        <v>1562.6</v>
+        <v>1626.4</v>
       </c>
       <c r="F50">
-        <v>3062.4</v>
+        <v>3126.2</v>
       </c>
       <c r="G50">
         <v>179.8</v>
@@ -5381,45 +5381,45 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M50">
-        <v>220.18656</v>
+        <v>236.96596</v>
       </c>
       <c r="N50">
-        <v>333.5950726530613</v>
+        <v>316.8156726530613</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>333.5950726530613</v>
+        <v>316.8156726530613</v>
       </c>
       <c r="Q50">
-        <v>693.8950726530612</v>
+        <v>677.1156726530612</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2667640886462576</v>
+        <v>0.2710967178353999</v>
       </c>
       <c r="T50">
-        <v>1.892730594740953</v>
+        <v>1.929842959343717</v>
       </c>
       <c r="U50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0</v>
       </c>
       <c r="W50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.515056471444312</v>
+        <v>2.33696701692117</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.175401326096054</v>
+        <v>0.1757013260960539</v>
       </c>
       <c r="C51">
-        <v>3230.687212166129</v>
+        <v>3152.621567469942</v>
       </c>
       <c r="D51">
-        <v>6177.087212166129</v>
+        <v>6162.821567469942</v>
       </c>
       <c r="E51">
-        <v>1626.4</v>
+        <v>1690.2</v>
       </c>
       <c r="F51">
-        <v>3126.2</v>
+        <v>3190</v>
       </c>
       <c r="G51">
         <v>179.8</v>
@@ -5463,28 +5463,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M51">
-        <v>236.96596</v>
+        <v>241.802</v>
       </c>
       <c r="N51">
-        <v>316.8156726530613</v>
+        <v>311.9796326530612</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>316.8156726530613</v>
+        <v>311.9796326530612</v>
       </c>
       <c r="Q51">
-        <v>677.1156726530612</v>
+        <v>672.2796326530612</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2710967178353999</v>
+        <v>0.2756026521921079</v>
       </c>
       <c r="T51">
-        <v>1.929842959343717</v>
+        <v>1.968439818530592</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.33696701692117</v>
+        <v>2.290227676582746</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1757013260960539</v>
+        <v>0.1760013260960539</v>
       </c>
       <c r="C52">
-        <v>3152.621567469942</v>
+        <v>3074.621662402332</v>
       </c>
       <c r="D52">
-        <v>6162.821567469942</v>
+        <v>6148.621662402332</v>
       </c>
       <c r="E52">
-        <v>1690.2</v>
+        <v>1754</v>
       </c>
       <c r="F52">
-        <v>3190</v>
+        <v>3253.8</v>
       </c>
       <c r="G52">
         <v>179.8</v>
@@ -5545,28 +5545,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M52">
-        <v>241.802</v>
+        <v>246.63804</v>
       </c>
       <c r="N52">
-        <v>311.9796326530612</v>
+        <v>307.1435926530612</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>311.9796326530612</v>
+        <v>307.1435926530612</v>
       </c>
       <c r="Q52">
-        <v>672.2796326530612</v>
+        <v>667.4435926530612</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2756026521921079</v>
+        <v>0.2802925022368448</v>
       </c>
       <c r="T52">
-        <v>1.968439818530592</v>
+        <v>2.008612059725094</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.290227676582746</v>
+        <v>2.245321251551712</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1760013260960539</v>
+        <v>0.176301326096054</v>
       </c>
       <c r="C53">
-        <v>3074.621662402332</v>
+        <v>2996.687043591156</v>
       </c>
       <c r="D53">
-        <v>6148.621662402332</v>
+        <v>6134.487043591155</v>
       </c>
       <c r="E53">
-        <v>1754</v>
+        <v>1817.8</v>
       </c>
       <c r="F53">
-        <v>3253.8</v>
+        <v>3317.6</v>
       </c>
       <c r="G53">
         <v>179.8</v>
@@ -5627,28 +5627,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M53">
-        <v>246.63804</v>
+        <v>251.47408</v>
       </c>
       <c r="N53">
-        <v>307.1435926530612</v>
+        <v>302.3075526530612</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>307.1435926530612</v>
+        <v>302.3075526530612</v>
       </c>
       <c r="Q53">
-        <v>667.4435926530612</v>
+        <v>662.6075526530612</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2802925022368448</v>
+        <v>0.2851777627001124</v>
       </c>
       <c r="T53">
-        <v>2.008612059725094</v>
+        <v>2.0504581443027</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.245321251551712</v>
+        <v>2.202141996714179</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.176301326096054</v>
+        <v>0.1766013260960539</v>
       </c>
       <c r="C54">
-        <v>2996.687043591156</v>
+        <v>2918.817261823608</v>
       </c>
       <c r="D54">
-        <v>6134.487043591155</v>
+        <v>6120.417261823608</v>
       </c>
       <c r="E54">
-        <v>1817.8</v>
+        <v>1881.6</v>
       </c>
       <c r="F54">
-        <v>3317.6</v>
+        <v>3381.4</v>
       </c>
       <c r="G54">
         <v>179.8</v>
@@ -5709,28 +5709,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M54">
-        <v>251.47408</v>
+        <v>256.31012</v>
       </c>
       <c r="N54">
-        <v>302.3075526530612</v>
+        <v>297.4715126530612</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>302.3075526530612</v>
+        <v>297.4715126530612</v>
       </c>
       <c r="Q54">
-        <v>662.6075526530612</v>
+        <v>657.7715126530611</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2851777627001124</v>
+        <v>0.2902709065873488</v>
       </c>
       <c r="T54">
-        <v>2.0504581443027</v>
+        <v>2.094084913330417</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.202141996714179</v>
+        <v>2.160592147719572</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1766013260960539</v>
+        <v>0.1769013260960539</v>
       </c>
       <c r="C55">
-        <v>2918.817261823608</v>
+        <v>2841.011871998628</v>
       </c>
       <c r="D55">
-        <v>6120.417261823608</v>
+        <v>6106.411871998628</v>
       </c>
       <c r="E55">
-        <v>1881.6</v>
+        <v>1945.4</v>
       </c>
       <c r="F55">
-        <v>3381.4</v>
+        <v>3445.2</v>
       </c>
       <c r="G55">
         <v>179.8</v>
@@ -5791,28 +5791,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M55">
-        <v>256.31012</v>
+        <v>261.1461600000001</v>
       </c>
       <c r="N55">
-        <v>297.4715126530612</v>
+        <v>292.6354726530612</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>297.4715126530612</v>
+        <v>292.6354726530612</v>
       </c>
       <c r="Q55">
-        <v>657.7715126530611</v>
+        <v>652.9354726530612</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2902709065873488</v>
+        <v>0.2955854915131608</v>
       </c>
       <c r="T55">
-        <v>2.094084913330417</v>
+        <v>2.139608498402817</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.160592147719572</v>
+        <v>2.120581182021061</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1769013260960539</v>
+        <v>0.1772013260960539</v>
       </c>
       <c r="C56">
-        <v>2841.011871998628</v>
+        <v>2763.270433079964</v>
       </c>
       <c r="D56">
-        <v>6106.411871998628</v>
+        <v>6092.470433079964</v>
       </c>
       <c r="E56">
-        <v>1945.4</v>
+        <v>2009.200000000001</v>
       </c>
       <c r="F56">
-        <v>3445.2</v>
+        <v>3509</v>
       </c>
       <c r="G56">
         <v>179.8</v>
@@ -5873,28 +5873,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M56">
-        <v>261.1461600000001</v>
+        <v>265.9822</v>
       </c>
       <c r="N56">
-        <v>292.6354726530612</v>
+        <v>287.7994326530612</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>292.6354726530612</v>
+        <v>287.7994326530612</v>
       </c>
       <c r="Q56">
-        <v>652.9354726530612</v>
+        <v>648.0994326530612</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2955854915131608</v>
+        <v>0.3011362802134532</v>
       </c>
       <c r="T56">
-        <v>2.139608498402817</v>
+        <v>2.18715535392288</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.120581182021061</v>
+        <v>2.082025160529769</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1772013260960539</v>
+        <v>0.177501326096054</v>
       </c>
       <c r="C57">
-        <v>2763.270433079964</v>
+        <v>2685.592508049876</v>
       </c>
       <c r="D57">
-        <v>6092.470433079964</v>
+        <v>6078.592508049876</v>
       </c>
       <c r="E57">
-        <v>2009.200000000001</v>
+        <v>2073</v>
       </c>
       <c r="F57">
-        <v>3509</v>
+        <v>3572.8</v>
       </c>
       <c r="G57">
         <v>179.8</v>
@@ -5955,28 +5955,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M57">
-        <v>265.9822</v>
+        <v>270.8182400000001</v>
       </c>
       <c r="N57">
-        <v>287.7994326530612</v>
+        <v>282.9633926530612</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>287.7994326530612</v>
+        <v>282.9633926530612</v>
       </c>
       <c r="Q57">
-        <v>648.0994326530612</v>
+        <v>643.2633926530611</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3011362802134532</v>
+        <v>0.3069393774910317</v>
       </c>
       <c r="T57">
-        <v>2.18715535392288</v>
+        <v>2.2368634301484</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.082025160529769</v>
+        <v>2.044846139806023</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.177501326096054</v>
+        <v>0.177801326096054</v>
       </c>
       <c r="C58">
-        <v>2685.592508049876</v>
+        <v>2607.977663863477</v>
       </c>
       <c r="D58">
-        <v>6078.592508049876</v>
+        <v>6064.777663863477</v>
       </c>
       <c r="E58">
-        <v>2073</v>
+        <v>2136.8</v>
       </c>
       <c r="F58">
-        <v>3572.8</v>
+        <v>3636.6</v>
       </c>
       <c r="G58">
         <v>179.8</v>
@@ -6037,28 +6037,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M58">
-        <v>270.8182400000001</v>
+        <v>275.65428</v>
       </c>
       <c r="N58">
-        <v>282.9633926530612</v>
+        <v>278.1273526530612</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>282.9633926530612</v>
+        <v>278.1273526530612</v>
       </c>
       <c r="Q58">
-        <v>643.2633926530611</v>
+        <v>638.4273526530612</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3069393774910317</v>
+        <v>0.313012386269893</v>
       </c>
       <c r="T58">
-        <v>2.2368634301484</v>
+        <v>2.288883509919293</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.044846139806023</v>
+        <v>2.008971646125216</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.177801326096054</v>
+        <v>0.186337326096054</v>
       </c>
       <c r="C59">
-        <v>2607.977663863477</v>
+        <v>2175.813304181866</v>
       </c>
       <c r="D59">
-        <v>6064.777663863477</v>
+        <v>5696.413304181867</v>
       </c>
       <c r="E59">
-        <v>2136.8</v>
+        <v>2200.6</v>
       </c>
       <c r="F59">
-        <v>3636.6</v>
+        <v>3700.400000000001</v>
       </c>
       <c r="G59">
         <v>179.8</v>
@@ -6119,45 +6119,45 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M59">
-        <v>275.65428</v>
+        <v>333.0360000000001</v>
       </c>
       <c r="N59">
-        <v>278.1273526530612</v>
+        <v>220.7456326530612</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>278.1273526530612</v>
+        <v>220.7456326530612</v>
       </c>
       <c r="Q59">
-        <v>638.4273526530612</v>
+        <v>581.0456326530611</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.313012386269893</v>
+        <v>0.3193745859429857</v>
       </c>
       <c r="T59">
-        <v>2.288883509919293</v>
+        <v>2.343380736345943</v>
       </c>
       <c r="U59">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V59">
         <v>0</v>
       </c>
       <c r="W59">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.008971646125216</v>
+        <v>1.662828140660653</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1863373260960539</v>
+        <v>0.186779326096054</v>
       </c>
       <c r="C60">
-        <v>2175.813304181868</v>
+        <v>2094.153843861189</v>
       </c>
       <c r="D60">
-        <v>5696.413304181868</v>
+        <v>5678.553843861188</v>
       </c>
       <c r="E60">
-        <v>2200.599999999999</v>
+        <v>2264.4</v>
       </c>
       <c r="F60">
-        <v>3700.4</v>
+        <v>3764.2</v>
       </c>
       <c r="G60">
         <v>179.8</v>
@@ -6201,28 +6201,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M60">
-        <v>333.0359999999999</v>
+        <v>338.778</v>
       </c>
       <c r="N60">
-        <v>220.7456326530613</v>
+        <v>215.0036326530613</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>220.7456326530613</v>
+        <v>215.0036326530613</v>
       </c>
       <c r="Q60">
-        <v>581.0456326530613</v>
+        <v>575.3036326530612</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3193745859429856</v>
+        <v>0.3260471368196438</v>
       </c>
       <c r="T60">
-        <v>2.343380736345942</v>
+        <v>2.400536364061697</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.662828140660653</v>
+        <v>1.634644612852846</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.186779326096054</v>
+        <v>0.1872213260960539</v>
       </c>
       <c r="C61">
-        <v>2094.153843861189</v>
+        <v>2012.606019906535</v>
       </c>
       <c r="D61">
-        <v>5678.553843861188</v>
+        <v>5660.806019906535</v>
       </c>
       <c r="E61">
-        <v>2264.4</v>
+        <v>2328.2</v>
       </c>
       <c r="F61">
-        <v>3764.2</v>
+        <v>3828</v>
       </c>
       <c r="G61">
         <v>179.8</v>
@@ -6283,28 +6283,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M61">
-        <v>338.778</v>
+        <v>344.52</v>
       </c>
       <c r="N61">
-        <v>215.0036326530613</v>
+        <v>209.2616326530613</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>215.0036326530613</v>
+        <v>209.2616326530613</v>
       </c>
       <c r="Q61">
-        <v>575.3036326530612</v>
+        <v>569.5616326530612</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3260471368196438</v>
+        <v>0.3330533152401349</v>
       </c>
       <c r="T61">
-        <v>2.400536364061697</v>
+        <v>2.46054977316324</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.634644612852846</v>
+        <v>1.607400535971965</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1872213260960539</v>
+        <v>0.1876633260960539</v>
       </c>
       <c r="C62">
-        <v>2012.606019906535</v>
+        <v>1931.168788850043</v>
       </c>
       <c r="D62">
-        <v>5660.806019906535</v>
+        <v>5643.168788850043</v>
       </c>
       <c r="E62">
-        <v>2328.2</v>
+        <v>2392</v>
       </c>
       <c r="F62">
-        <v>3828</v>
+        <v>3891.8</v>
       </c>
       <c r="G62">
         <v>179.8</v>
@@ -6365,28 +6365,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M62">
-        <v>344.52</v>
+        <v>350.2619999999999</v>
       </c>
       <c r="N62">
-        <v>209.2616326530613</v>
+        <v>203.5196326530613</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>209.2616326530613</v>
+        <v>203.5196326530613</v>
       </c>
       <c r="Q62">
-        <v>569.5616326530612</v>
+        <v>563.8196326530613</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3330533152401349</v>
+        <v>0.3404187848616768</v>
       </c>
       <c r="T62">
-        <v>2.46054977316324</v>
+        <v>2.523640792987938</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.607400535971965</v>
+        <v>1.581049707513408</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1876633260960539</v>
+        <v>0.1881053260960539</v>
       </c>
       <c r="C63">
-        <v>1931.168788850043</v>
+        <v>1849.841120187887</v>
       </c>
       <c r="D63">
-        <v>5643.168788850043</v>
+        <v>5625.641120187886</v>
       </c>
       <c r="E63">
-        <v>2392</v>
+        <v>2455.8</v>
       </c>
       <c r="F63">
-        <v>3891.8</v>
+        <v>3955.6</v>
       </c>
       <c r="G63">
         <v>179.8</v>
@@ -6447,28 +6447,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M63">
-        <v>350.2619999999999</v>
+        <v>356.004</v>
       </c>
       <c r="N63">
-        <v>203.5196326530613</v>
+        <v>197.7776326530613</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>203.5196326530613</v>
+        <v>197.7776326530613</v>
       </c>
       <c r="Q63">
-        <v>563.8196326530613</v>
+        <v>558.0776326530613</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3404187848616768</v>
+        <v>0.3481719107790893</v>
       </c>
       <c r="T63">
-        <v>2.523640792987938</v>
+        <v>2.59005239280341</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.581049707513408</v>
+        <v>1.555548905779321</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1881053260960539</v>
+        <v>0.1885473260960539</v>
       </c>
       <c r="C64">
-        <v>1849.841120187887</v>
+        <v>1768.621996179568</v>
       </c>
       <c r="D64">
-        <v>5625.641120187886</v>
+        <v>5608.221996179568</v>
       </c>
       <c r="E64">
-        <v>2455.8</v>
+        <v>2519.6</v>
       </c>
       <c r="F64">
-        <v>3955.6</v>
+        <v>4019.4</v>
       </c>
       <c r="G64">
         <v>179.8</v>
@@ -6529,28 +6529,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M64">
-        <v>356.004</v>
+        <v>361.746</v>
       </c>
       <c r="N64">
-        <v>197.7776326530613</v>
+        <v>192.0356326530613</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>197.7776326530613</v>
+        <v>192.0356326530613</v>
       </c>
       <c r="Q64">
-        <v>558.0776326530613</v>
+        <v>552.3356326530612</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3481719107790893</v>
+        <v>0.3563441245839296</v>
       </c>
       <c r="T64">
-        <v>2.59005239280341</v>
+        <v>2.660053808825124</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.555548905779321</v>
+        <v>1.530857653306633</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1885473260960539</v>
+        <v>0.188989326096054</v>
       </c>
       <c r="C65">
-        <v>1768.621996179568</v>
+        <v>1687.510411650923</v>
       </c>
       <c r="D65">
-        <v>5608.221996179568</v>
+        <v>5590.910411650923</v>
       </c>
       <c r="E65">
-        <v>2519.6</v>
+        <v>2583.400000000001</v>
       </c>
       <c r="F65">
-        <v>4019.4</v>
+        <v>4083.2</v>
       </c>
       <c r="G65">
         <v>179.8</v>
@@ -6611,28 +6611,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M65">
-        <v>361.746</v>
+        <v>367.488</v>
       </c>
       <c r="N65">
-        <v>192.0356326530613</v>
+        <v>186.2936326530613</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>192.0356326530613</v>
+        <v>186.2936326530613</v>
       </c>
       <c r="Q65">
-        <v>552.3356326530612</v>
+        <v>546.5936326530611</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3563441245839296</v>
+        <v>0.3649703502668165</v>
       </c>
       <c r="T65">
-        <v>2.660053808825124</v>
+        <v>2.733944192403599</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.530857653306633</v>
+        <v>1.506938002473717</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.188989326096054</v>
+        <v>0.226351326096054</v>
       </c>
       <c r="C66">
-        <v>1687.510411650923</v>
+        <v>466.7674009472912</v>
       </c>
       <c r="D66">
-        <v>5590.910411650923</v>
+        <v>4433.967400947291</v>
       </c>
       <c r="E66">
-        <v>2583.400000000001</v>
+        <v>2647.2</v>
       </c>
       <c r="F66">
-        <v>4083.2</v>
+        <v>4147</v>
       </c>
       <c r="G66">
         <v>179.8</v>
@@ -6693,45 +6693,45 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M66">
-        <v>367.488</v>
+        <v>608.7796000000001</v>
       </c>
       <c r="N66">
-        <v>186.2936326530613</v>
+        <v>-54.99796734693882</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P66">
-        <v>186.2936326530613</v>
+        <v>-54.99796734693882</v>
       </c>
       <c r="Q66">
-        <v>546.5936326530611</v>
+        <v>305.3020326530611</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3649703502668165</v>
+        <v>0.3740895031315828</v>
       </c>
       <c r="T66">
-        <v>2.733944192403599</v>
+        <v>2.812056883615132</v>
       </c>
       <c r="U66">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V66">
         <v>0</v>
       </c>
       <c r="W66">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.506938002473717</v>
+        <v>0.9096586558634048</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.226351326096054</v>
+        <v>0.227361326096054</v>
       </c>
       <c r="C67">
-        <v>466.7674009472912</v>
+        <v>378.3018668754175</v>
       </c>
       <c r="D67">
-        <v>4433.967400947291</v>
+        <v>4409.301866875418</v>
       </c>
       <c r="E67">
-        <v>2647.2</v>
+        <v>2711</v>
       </c>
       <c r="F67">
-        <v>4147</v>
+        <v>4210.8</v>
       </c>
       <c r="G67">
         <v>179.8</v>
@@ -6775,28 +6775,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M67">
-        <v>608.7796000000001</v>
+        <v>618.1454400000001</v>
       </c>
       <c r="N67">
-        <v>-54.99796734693882</v>
+        <v>-64.36380734693887</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-54.99796734693882</v>
+        <v>-64.36380734693887</v>
       </c>
       <c r="Q67">
-        <v>305.3020326530611</v>
+        <v>295.9361926530611</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3740895031315828</v>
+        <v>0.3837450767530999</v>
       </c>
       <c r="T67">
-        <v>2.812056883615132</v>
+        <v>2.894764439015576</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9096586558634048</v>
+        <v>0.8958759489563833</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.227361326096054</v>
+        <v>0.228371326096054</v>
       </c>
       <c r="C68">
-        <v>378.3018668754175</v>
+        <v>290.1092364401147</v>
       </c>
       <c r="D68">
-        <v>4409.301866875418</v>
+        <v>4384.909236440115</v>
       </c>
       <c r="E68">
-        <v>2711</v>
+        <v>2774.8</v>
       </c>
       <c r="F68">
-        <v>4210.8</v>
+        <v>4274.6</v>
       </c>
       <c r="G68">
         <v>179.8</v>
@@ -6857,28 +6857,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M68">
-        <v>618.1454400000001</v>
+        <v>627.5112800000001</v>
       </c>
       <c r="N68">
-        <v>-64.36380734693887</v>
+        <v>-73.7296473469388</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-64.36380734693887</v>
+        <v>-73.7296473469388</v>
       </c>
       <c r="Q68">
-        <v>295.9361926530611</v>
+        <v>286.5703526530611</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3837450767530999</v>
+        <v>0.393985836654709</v>
       </c>
       <c r="T68">
-        <v>2.894764439015576</v>
+        <v>2.9824845735312</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8958759489563833</v>
+        <v>0.882504666136139</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.228371326096054</v>
+        <v>0.2293813260960539</v>
       </c>
       <c r="C69">
-        <v>290.1092364401147</v>
+        <v>202.1850053814114</v>
       </c>
       <c r="D69">
-        <v>4384.909236440115</v>
+        <v>4360.785005381412</v>
       </c>
       <c r="E69">
-        <v>2774.8</v>
+        <v>2838.6</v>
       </c>
       <c r="F69">
-        <v>4274.6</v>
+        <v>4338.400000000001</v>
       </c>
       <c r="G69">
         <v>179.8</v>
@@ -6939,28 +6939,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M69">
-        <v>627.5112800000001</v>
+        <v>636.8771200000001</v>
       </c>
       <c r="N69">
-        <v>-73.7296473469388</v>
+        <v>-83.09548734693885</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-73.7296473469388</v>
+        <v>-83.09548734693885</v>
       </c>
       <c r="Q69">
-        <v>286.5703526530611</v>
+        <v>277.2045126530611</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.393985836654709</v>
+        <v>0.4048666440501686</v>
       </c>
       <c r="T69">
-        <v>2.9824845735312</v>
+        <v>3.07568721645405</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.882504666136139</v>
+        <v>0.8695266563400192</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2293813260960539</v>
+        <v>0.230391326096054</v>
       </c>
       <c r="C70">
-        <v>202.1850053814114</v>
+        <v>114.524768020402</v>
       </c>
       <c r="D70">
-        <v>4360.785005381412</v>
+        <v>4336.924768020403</v>
       </c>
       <c r="E70">
-        <v>2838.6</v>
+        <v>2902.400000000001</v>
       </c>
       <c r="F70">
-        <v>4338.400000000001</v>
+        <v>4402.200000000001</v>
       </c>
       <c r="G70">
         <v>179.8</v>
@@ -7021,28 +7021,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M70">
-        <v>636.8771200000001</v>
+        <v>646.2429600000002</v>
       </c>
       <c r="N70">
-        <v>-83.09548734693885</v>
+        <v>-92.4613273469389</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-83.09548734693885</v>
+        <v>-92.4613273469389</v>
       </c>
       <c r="Q70">
-        <v>277.2045126530611</v>
+        <v>267.8386726530611</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4048666440501686</v>
+        <v>0.416449439019529</v>
       </c>
       <c r="T70">
-        <v>3.07568721645405</v>
+        <v>3.174902933113859</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8695266563400192</v>
+        <v>0.8569248207408884</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.230391326096054</v>
+        <v>0.231401326096054</v>
       </c>
       <c r="C71">
-        <v>114.524768020402</v>
+        <v>27.12421457697656</v>
       </c>
       <c r="D71">
-        <v>4336.924768020403</v>
+        <v>4313.324214576976</v>
       </c>
       <c r="E71">
-        <v>2902.400000000001</v>
+        <v>2966.2</v>
       </c>
       <c r="F71">
-        <v>4402.200000000001</v>
+        <v>4466</v>
       </c>
       <c r="G71">
         <v>179.8</v>
@@ -7103,28 +7103,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M71">
-        <v>646.2429600000002</v>
+        <v>655.6088000000001</v>
       </c>
       <c r="N71">
-        <v>-92.4613273469389</v>
+        <v>-101.8271673469388</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-92.4613273469389</v>
+        <v>-101.8271673469388</v>
       </c>
       <c r="Q71">
-        <v>267.8386726530611</v>
+        <v>258.4728326530611</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.416449439019529</v>
+        <v>0.4288044203201799</v>
       </c>
       <c r="T71">
-        <v>3.174902933113859</v>
+        <v>3.28073303088432</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8569248207408884</v>
+        <v>0.8446830375874472</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.231401326096054</v>
+        <v>0.2324113260960539</v>
       </c>
       <c r="C72">
-        <v>27.12421457697656</v>
+        <v>-60.02087142536129</v>
       </c>
       <c r="D72">
-        <v>4313.324214576976</v>
+        <v>4289.979128574639</v>
       </c>
       <c r="E72">
-        <v>2966.2</v>
+        <v>3030</v>
       </c>
       <c r="F72">
-        <v>4466</v>
+        <v>4529.8</v>
       </c>
       <c r="G72">
         <v>179.8</v>
@@ -7185,28 +7185,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M72">
-        <v>655.6088000000001</v>
+        <v>664.9746400000001</v>
       </c>
       <c r="N72">
-        <v>-101.8271673469388</v>
+        <v>-111.1930073469389</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-101.8271673469388</v>
+        <v>-111.1930073469389</v>
       </c>
       <c r="Q72">
-        <v>258.4728326530611</v>
+        <v>249.1069926530611</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4288044203201799</v>
+        <v>0.4420114692967378</v>
       </c>
       <c r="T72">
-        <v>3.28073303088432</v>
+        <v>3.393861756087228</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8446830375874472</v>
+        <v>0.8327860933960747</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.232411326096054</v>
+        <v>0.233421326096054</v>
       </c>
       <c r="C73">
-        <v>-60.02087142536129</v>
+        <v>-146.914615670843</v>
       </c>
       <c r="D73">
-        <v>4289.979128574639</v>
+        <v>4266.885384329156</v>
       </c>
       <c r="E73">
-        <v>3030</v>
+        <v>3093.799999999999</v>
       </c>
       <c r="F73">
-        <v>4529.8</v>
+        <v>4593.599999999999</v>
       </c>
       <c r="G73">
         <v>179.8</v>
@@ -7267,28 +7267,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M73">
-        <v>664.9746400000001</v>
+        <v>674.34048</v>
       </c>
       <c r="N73">
-        <v>-111.1930073469389</v>
+        <v>-120.5588473469387</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-111.1930073469389</v>
+        <v>-120.5588473469387</v>
       </c>
       <c r="Q73">
-        <v>249.1069926530611</v>
+        <v>239.7411526530612</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4420114692967377</v>
+        <v>0.4561618789144784</v>
       </c>
       <c r="T73">
-        <v>3.393861756087227</v>
+        <v>3.515071104518914</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8327860933960747</v>
+        <v>0.821219619876685</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.233421326096054</v>
+        <v>0.234431326096054</v>
       </c>
       <c r="C74">
-        <v>-146.914615670843</v>
+        <v>-233.5610554821069</v>
       </c>
       <c r="D74">
-        <v>4266.885384329156</v>
+        <v>4244.038944517893</v>
       </c>
       <c r="E74">
-        <v>3093.799999999999</v>
+        <v>3157.599999999999</v>
       </c>
       <c r="F74">
-        <v>4593.599999999999</v>
+        <v>4657.4</v>
       </c>
       <c r="G74">
         <v>179.8</v>
@@ -7349,28 +7349,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M74">
-        <v>674.34048</v>
+        <v>683.70632</v>
       </c>
       <c r="N74">
-        <v>-120.5588473469387</v>
+        <v>-129.9246873469388</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-120.5588473469387</v>
+        <v>-129.9246873469388</v>
       </c>
       <c r="Q74">
-        <v>239.7411526530612</v>
+        <v>230.3753126530612</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4561618789144784</v>
+        <v>0.471360467022422</v>
       </c>
       <c r="T74">
-        <v>3.515071104518914</v>
+        <v>3.645258923204799</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.821219619876685</v>
+        <v>0.8099700360427577</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.234431326096054</v>
+        <v>0.2754013260960539</v>
       </c>
       <c r="C75">
-        <v>-233.5610554821069</v>
+        <v>-1054.666244059964</v>
       </c>
       <c r="D75">
-        <v>4244.038944517893</v>
+        <v>3486.733755940036</v>
       </c>
       <c r="E75">
-        <v>3157.599999999999</v>
+        <v>3221.4</v>
       </c>
       <c r="F75">
-        <v>4657.4</v>
+        <v>4721.2</v>
       </c>
       <c r="G75">
         <v>179.8</v>
@@ -7431,45 +7431,45 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M75">
-        <v>683.70632</v>
+        <v>948.01696</v>
       </c>
       <c r="N75">
-        <v>-129.9246873469388</v>
+        <v>-394.2353273469388</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-129.9246873469388</v>
+        <v>-394.2353273469388</v>
       </c>
       <c r="Q75">
-        <v>230.3753126530612</v>
+        <v>-33.93532734693883</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.471360467022422</v>
+        <v>0.4877281772925151</v>
       </c>
       <c r="T75">
-        <v>3.645258923204799</v>
+        <v>3.785461189481907</v>
       </c>
       <c r="U75">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
         <v>0</v>
       </c>
       <c r="W75">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.8099700360427577</v>
+        <v>0.5841473897819942</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2754013260960539</v>
+        <v>0.276951326096054</v>
       </c>
       <c r="C76">
-        <v>-1054.666244059964</v>
+        <v>-1141.846760248139</v>
       </c>
       <c r="D76">
-        <v>3486.733755940036</v>
+        <v>3463.353239751861</v>
       </c>
       <c r="E76">
-        <v>3221.4</v>
+        <v>3285.2</v>
       </c>
       <c r="F76">
-        <v>4721.2</v>
+        <v>4785</v>
       </c>
       <c r="G76">
         <v>179.8</v>
@@ -7513,28 +7513,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M76">
-        <v>948.01696</v>
+        <v>960.828</v>
       </c>
       <c r="N76">
-        <v>-394.2353273469388</v>
+        <v>-407.0463673469387</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-394.2353273469388</v>
+        <v>-407.0463673469387</v>
       </c>
       <c r="Q76">
-        <v>-33.93532734693883</v>
+        <v>-46.74636734693877</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4877281772925151</v>
+        <v>0.5054053043842158</v>
       </c>
       <c r="T76">
-        <v>3.785461189481907</v>
+        <v>3.936879637061184</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5841473897819942</v>
+        <v>0.5763587579182343</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.276951326096054</v>
+        <v>0.2785013260960539</v>
       </c>
       <c r="C77">
-        <v>-1141.846760248139</v>
+        <v>-1228.715805928608</v>
       </c>
       <c r="D77">
-        <v>3463.353239751861</v>
+        <v>3440.284194071392</v>
       </c>
       <c r="E77">
-        <v>3285.2</v>
+        <v>3349</v>
       </c>
       <c r="F77">
-        <v>4785</v>
+        <v>4848.8</v>
       </c>
       <c r="G77">
         <v>179.8</v>
@@ -7595,28 +7595,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M77">
-        <v>960.828</v>
+        <v>973.63904</v>
       </c>
       <c r="N77">
-        <v>-407.0463673469387</v>
+        <v>-419.8574073469388</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-407.0463673469387</v>
+        <v>-419.8574073469388</v>
       </c>
       <c r="Q77">
-        <v>-46.74636734693877</v>
+        <v>-59.55740734693882</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5054053043842158</v>
+        <v>0.5245555254002248</v>
       </c>
       <c r="T77">
-        <v>3.936879637061184</v>
+        <v>4.1009162886054</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5763587579182343</v>
+        <v>0.5687750900508891</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2785013260960539</v>
+        <v>0.2800513260960539</v>
       </c>
       <c r="C78">
-        <v>-1228.715805928608</v>
+        <v>-1315.279563938771</v>
       </c>
       <c r="D78">
-        <v>3440.284194071392</v>
+        <v>3417.520436061229</v>
       </c>
       <c r="E78">
-        <v>3349</v>
+        <v>3412.8</v>
       </c>
       <c r="F78">
-        <v>4848.8</v>
+        <v>4912.6</v>
       </c>
       <c r="G78">
         <v>179.8</v>
@@ -7677,28 +7677,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M78">
-        <v>973.63904</v>
+        <v>986.4500800000001</v>
       </c>
       <c r="N78">
-        <v>-419.8574073469388</v>
+        <v>-432.6684473469388</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-419.8574073469388</v>
+        <v>-432.6684473469388</v>
       </c>
       <c r="Q78">
-        <v>-59.55740734693882</v>
+        <v>-72.36844734693886</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5245555254002248</v>
+        <v>0.5453709830263215</v>
       </c>
       <c r="T78">
-        <v>4.1009162886054</v>
+        <v>4.279216996805634</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5687750900508891</v>
+        <v>0.5613884005697087</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2800513260960539</v>
+        <v>0.2816013260960539</v>
       </c>
       <c r="C79">
-        <v>-1315.279563938771</v>
+        <v>-1401.544054548707</v>
       </c>
       <c r="D79">
-        <v>3417.520436061229</v>
+        <v>3395.055945451294</v>
       </c>
       <c r="E79">
-        <v>3412.8</v>
+        <v>3476.6</v>
       </c>
       <c r="F79">
-        <v>4912.6</v>
+        <v>4976.400000000001</v>
       </c>
       <c r="G79">
         <v>179.8</v>
@@ -7759,28 +7759,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M79">
-        <v>986.4500800000001</v>
+        <v>999.2611200000001</v>
       </c>
       <c r="N79">
-        <v>-432.6684473469388</v>
+        <v>-445.4794873469389</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-432.6684473469388</v>
+        <v>-445.4794873469389</v>
       </c>
       <c r="Q79">
-        <v>-72.36844734693886</v>
+        <v>-85.17948734693891</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5453709830263215</v>
+        <v>0.5680787549820634</v>
       </c>
       <c r="T79">
-        <v>4.279216996805634</v>
+        <v>4.4737268602968</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5613884005697087</v>
+        <v>0.5541911133829176</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2816013260960539</v>
+        <v>0.283151326096054</v>
       </c>
       <c r="C80">
-        <v>-1401.544054548707</v>
+        <v>-1487.515140769307</v>
       </c>
       <c r="D80">
-        <v>3395.055945451294</v>
+        <v>3372.884859230692</v>
       </c>
       <c r="E80">
-        <v>3476.6</v>
+        <v>3540.4</v>
       </c>
       <c r="F80">
-        <v>4976.400000000001</v>
+        <v>5040.2</v>
       </c>
       <c r="G80">
         <v>179.8</v>
@@ -7841,28 +7841,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M80">
-        <v>999.2611200000001</v>
+        <v>1012.07216</v>
       </c>
       <c r="N80">
-        <v>-445.4794873469389</v>
+        <v>-458.2905273469387</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-445.4794873469389</v>
+        <v>-458.2905273469387</v>
       </c>
       <c r="Q80">
-        <v>-85.17948734693891</v>
+        <v>-97.99052734693873</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5680787549820634</v>
+        <v>0.5929491718859713</v>
       </c>
       <c r="T80">
-        <v>4.4737268602968</v>
+        <v>4.686761472691886</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5541911133829176</v>
+        <v>0.5471760359983238</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.283151326096054</v>
+        <v>0.2847013260960539</v>
       </c>
       <c r="C81">
-        <v>-1487.515140769307</v>
+        <v>-1573.198533453806</v>
       </c>
       <c r="D81">
-        <v>3372.884859230692</v>
+        <v>3351.001466546194</v>
       </c>
       <c r="E81">
-        <v>3540.4</v>
+        <v>3604.2</v>
       </c>
       <c r="F81">
-        <v>5040.2</v>
+        <v>5104</v>
       </c>
       <c r="G81">
         <v>179.8</v>
@@ -7923,28 +7923,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M81">
-        <v>1012.07216</v>
+        <v>1024.8832</v>
       </c>
       <c r="N81">
-        <v>-458.2905273469387</v>
+        <v>-471.1015673469387</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-458.2905273469387</v>
+        <v>-471.1015673469387</v>
       </c>
       <c r="Q81">
-        <v>-97.99052734693873</v>
+        <v>-110.8015673469388</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5929491718859713</v>
+        <v>0.6203066304802698</v>
       </c>
       <c r="T81">
-        <v>4.686761472691886</v>
+        <v>4.92109954632648</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5471760359983238</v>
+        <v>0.5403363355483447</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2847013260960539</v>
+        <v>0.2862513260960539</v>
       </c>
       <c r="C82">
-        <v>-1573.198533453806</v>
+        <v>-1658.599796201975</v>
       </c>
       <c r="D82">
-        <v>3351.001466546194</v>
+        <v>3329.400203798025</v>
       </c>
       <c r="E82">
-        <v>3604.2</v>
+        <v>3668</v>
       </c>
       <c r="F82">
-        <v>5104</v>
+        <v>5167.8</v>
       </c>
       <c r="G82">
         <v>179.8</v>
@@ -8005,28 +8005,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M82">
-        <v>1024.8832</v>
+        <v>1037.69424</v>
       </c>
       <c r="N82">
-        <v>-471.1015673469387</v>
+        <v>-483.9126073469388</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-471.1015673469387</v>
+        <v>-483.9126073469388</v>
       </c>
       <c r="Q82">
-        <v>-110.8015673469388</v>
+        <v>-123.6126073469388</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6203066304802698</v>
+        <v>0.6505438215581787</v>
       </c>
       <c r="T82">
-        <v>4.92109954632648</v>
+        <v>5.180104785606821</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5403363355483447</v>
+        <v>0.5336655165909576</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2862513260960539</v>
+        <v>0.287801326096054</v>
       </c>
       <c r="C83">
-        <v>-1658.599796201975</v>
+        <v>-1743.724350075861</v>
       </c>
       <c r="D83">
-        <v>3329.400203798025</v>
+        <v>3308.075649924139</v>
       </c>
       <c r="E83">
-        <v>3668</v>
+        <v>3731.8</v>
       </c>
       <c r="F83">
-        <v>5167.8</v>
+        <v>5231.6</v>
       </c>
       <c r="G83">
         <v>179.8</v>
@@ -8087,28 +8087,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M83">
-        <v>1037.69424</v>
+        <v>1050.50528</v>
       </c>
       <c r="N83">
-        <v>-483.9126073469388</v>
+        <v>-496.7236473469388</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-483.9126073469388</v>
+        <v>-496.7236473469388</v>
       </c>
       <c r="Q83">
-        <v>-123.6126073469388</v>
+        <v>-136.4236473469389</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6505438215581787</v>
+        <v>0.6841407005336332</v>
       </c>
       <c r="T83">
-        <v>5.180104785606821</v>
+        <v>5.467888384807201</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5336655165909576</v>
+        <v>0.5271574005349704</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.287801326096054</v>
+        <v>0.289351326096054</v>
       </c>
       <c r="C84">
-        <v>-1743.724350075861</v>
+        <v>-1828.577478135448</v>
       </c>
       <c r="D84">
-        <v>3308.075649924139</v>
+        <v>3287.022521864552</v>
       </c>
       <c r="E84">
-        <v>3731.8</v>
+        <v>3795.6</v>
       </c>
       <c r="F84">
-        <v>5231.6</v>
+        <v>5295.400000000001</v>
       </c>
       <c r="G84">
         <v>179.8</v>
@@ -8169,28 +8169,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M84">
-        <v>1050.50528</v>
+        <v>1063.31632</v>
       </c>
       <c r="N84">
-        <v>-496.7236473469388</v>
+        <v>-509.5346873469389</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-496.7236473469388</v>
+        <v>-509.5346873469389</v>
       </c>
       <c r="Q84">
-        <v>-136.4236473469389</v>
+        <v>-149.2346873469389</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6841407005336332</v>
+        <v>0.7216901535061999</v>
       </c>
       <c r="T84">
-        <v>5.467888384807201</v>
+        <v>5.789528878031154</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5271574005349704</v>
+        <v>0.5208061065526213</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.289351326096054</v>
+        <v>0.290901326096054</v>
       </c>
       <c r="C85">
-        <v>-1828.577478135448</v>
+        <v>-1913.16432980223</v>
       </c>
       <c r="D85">
-        <v>3287.022521864552</v>
+        <v>3266.235670197771</v>
       </c>
       <c r="E85">
-        <v>3795.6</v>
+        <v>3859.400000000001</v>
       </c>
       <c r="F85">
-        <v>5295.400000000001</v>
+        <v>5359.200000000001</v>
       </c>
       <c r="G85">
         <v>179.8</v>
@@ -8251,28 +8251,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M85">
-        <v>1063.31632</v>
+        <v>1076.12736</v>
       </c>
       <c r="N85">
-        <v>-509.5346873469389</v>
+        <v>-522.3457273469389</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-509.5346873469389</v>
+        <v>-522.3457273469389</v>
       </c>
       <c r="Q85">
-        <v>-149.2346873469389</v>
+        <v>-162.045727346939</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7216901535061999</v>
+        <v>0.7639332881003376</v>
       </c>
       <c r="T85">
-        <v>5.789528878031154</v>
+        <v>6.151374432908103</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5208061065526213</v>
+        <v>0.5146060338555662</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2909013260960539</v>
+        <v>0.292451326096054</v>
       </c>
       <c r="C86">
-        <v>-1913.164329802227</v>
+        <v>-1997.489925058242</v>
       </c>
       <c r="D86">
-        <v>3266.235670197772</v>
+        <v>3245.710074941758</v>
       </c>
       <c r="E86">
-        <v>3859.4</v>
+        <v>3923.2</v>
       </c>
       <c r="F86">
-        <v>5359.2</v>
+        <v>5423</v>
       </c>
       <c r="G86">
         <v>179.8</v>
@@ -8333,28 +8333,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M86">
-        <v>1076.12736</v>
+        <v>1088.9384</v>
       </c>
       <c r="N86">
-        <v>-522.3457273469387</v>
+        <v>-535.1567673469388</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-522.3457273469387</v>
+        <v>-535.1567673469388</v>
       </c>
       <c r="Q86">
-        <v>-162.0457273469387</v>
+        <v>-174.8567673469388</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.763933288100337</v>
+        <v>0.8118088406403595</v>
       </c>
       <c r="T86">
-        <v>6.151374432908098</v>
+        <v>6.561466061768638</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5146060338555664</v>
+        <v>0.5085518452219715</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.292451326096054</v>
+        <v>0.2940013260960539</v>
       </c>
       <c r="C87">
-        <v>-1997.489925058242</v>
+        <v>-2081.559158487771</v>
       </c>
       <c r="D87">
-        <v>3245.710074941758</v>
+        <v>3225.440841512229</v>
       </c>
       <c r="E87">
-        <v>3923.2</v>
+        <v>3987</v>
       </c>
       <c r="F87">
-        <v>5423</v>
+        <v>5486.8</v>
       </c>
       <c r="G87">
         <v>179.8</v>
@@ -8415,28 +8415,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M87">
-        <v>1088.9384</v>
+        <v>1101.74944</v>
       </c>
       <c r="N87">
-        <v>-535.1567673469388</v>
+        <v>-547.9678073469388</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-535.1567673469388</v>
+        <v>-547.9678073469388</v>
       </c>
       <c r="Q87">
-        <v>-174.8567673469388</v>
+        <v>-187.6678073469388</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8118088406403595</v>
+        <v>0.8665237578289567</v>
       </c>
       <c r="T87">
-        <v>6.561466061768638</v>
+        <v>7.030142209037828</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5085518452219715</v>
+        <v>0.5026384516728788</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2940013260960539</v>
+        <v>0.3260013260960539</v>
       </c>
       <c r="C88">
-        <v>-2081.559158487771</v>
+        <v>-2513.716112276809</v>
       </c>
       <c r="D88">
-        <v>3225.440841512229</v>
+        <v>2857.083887723191</v>
       </c>
       <c r="E88">
-        <v>3987</v>
+        <v>4050.8</v>
       </c>
       <c r="F88">
-        <v>5486.8</v>
+        <v>5550.6</v>
       </c>
       <c r="G88">
         <v>179.8</v>
@@ -8497,45 +8497,45 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M88">
-        <v>1101.74944</v>
+        <v>1308.83148</v>
       </c>
       <c r="N88">
-        <v>-547.9678073469388</v>
+        <v>-755.0498473469388</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-547.9678073469388</v>
+        <v>-755.0498473469388</v>
       </c>
       <c r="Q88">
-        <v>-187.6678073469388</v>
+        <v>-394.7498473469389</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8665237578289567</v>
+        <v>0.9296563545850302</v>
       </c>
       <c r="T88">
-        <v>7.030142209037828</v>
+        <v>7.570922378963814</v>
       </c>
       <c r="U88">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
         <v>0</v>
       </c>
       <c r="W88">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.5026384516728788</v>
+        <v>0.4231114861731942</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3260013260960539</v>
+        <v>0.327901326096054</v>
       </c>
       <c r="C89">
-        <v>-2513.716112276809</v>
+        <v>-2596.75905403039</v>
       </c>
       <c r="D89">
-        <v>2857.083887723191</v>
+        <v>2837.84094596961</v>
       </c>
       <c r="E89">
-        <v>4050.8</v>
+        <v>4114.599999999999</v>
       </c>
       <c r="F89">
-        <v>5550.6</v>
+        <v>5614.4</v>
       </c>
       <c r="G89">
         <v>179.8</v>
@@ -8579,28 +8579,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M89">
-        <v>1308.83148</v>
+        <v>1323.87552</v>
       </c>
       <c r="N89">
-        <v>-755.0498473469388</v>
+        <v>-770.0938873469388</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-755.0498473469388</v>
+        <v>-770.0938873469388</v>
       </c>
       <c r="Q89">
-        <v>-394.7498473469389</v>
+        <v>-409.7938873469388</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9296563545850302</v>
+        <v>1.00331105080045</v>
       </c>
       <c r="T89">
-        <v>7.570922378963814</v>
+        <v>8.2018325772108</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4231114861731942</v>
+        <v>0.4183034011030442</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.327901326096054</v>
+        <v>0.3298013260960539</v>
       </c>
       <c r="C90">
-        <v>-2596.75905403039</v>
+        <v>-2679.544521005</v>
       </c>
       <c r="D90">
-        <v>2837.84094596961</v>
+        <v>2818.855478994999</v>
       </c>
       <c r="E90">
-        <v>4114.599999999999</v>
+        <v>4178.4</v>
       </c>
       <c r="F90">
-        <v>5614.4</v>
+        <v>5678.2</v>
       </c>
       <c r="G90">
         <v>179.8</v>
@@ -8661,28 +8661,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M90">
-        <v>1323.87552</v>
+        <v>1338.91956</v>
       </c>
       <c r="N90">
-        <v>-770.0938873469388</v>
+        <v>-785.1379273469388</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-770.0938873469388</v>
+        <v>-785.1379273469388</v>
       </c>
       <c r="Q90">
-        <v>-409.7938873469388</v>
+        <v>-424.8379273469388</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.00331105080045</v>
+        <v>1.090357509964127</v>
       </c>
       <c r="T90">
-        <v>8.2018325772108</v>
+        <v>8.9474537205936</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4183034011030442</v>
+        <v>0.4136033628884033</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3298013260960539</v>
+        <v>0.331701326096054</v>
       </c>
       <c r="C91">
-        <v>-2679.544521005</v>
+        <v>-2762.077646462037</v>
       </c>
       <c r="D91">
-        <v>2818.855478994999</v>
+        <v>2800.122353537963</v>
       </c>
       <c r="E91">
-        <v>4178.4</v>
+        <v>4242.2</v>
       </c>
       <c r="F91">
-        <v>5678.2</v>
+        <v>5742</v>
       </c>
       <c r="G91">
         <v>179.8</v>
@@ -8743,28 +8743,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M91">
-        <v>1338.91956</v>
+        <v>1353.9636</v>
       </c>
       <c r="N91">
-        <v>-785.1379273469388</v>
+        <v>-800.1819673469388</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-785.1379273469388</v>
+        <v>-800.1819673469388</v>
       </c>
       <c r="Q91">
-        <v>-424.8379273469388</v>
+        <v>-439.8819673469388</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.090357509964127</v>
+        <v>1.19481326096054</v>
       </c>
       <c r="T91">
-        <v>8.9474537205936</v>
+        <v>9.84219909265296</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4136033628884033</v>
+        <v>0.4090077699674211</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.331701326096054</v>
+        <v>0.333601326096054</v>
       </c>
       <c r="C92">
-        <v>-2762.077646462037</v>
+        <v>-2844.363428108319</v>
       </c>
       <c r="D92">
-        <v>2800.122353537963</v>
+        <v>2781.636571891681</v>
       </c>
       <c r="E92">
-        <v>4242.2</v>
+        <v>4306</v>
       </c>
       <c r="F92">
-        <v>5742</v>
+        <v>5805.8</v>
       </c>
       <c r="G92">
         <v>179.8</v>
@@ -8825,28 +8825,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M92">
-        <v>1353.9636</v>
+        <v>1369.00764</v>
       </c>
       <c r="N92">
-        <v>-800.1819673469388</v>
+        <v>-815.2260073469388</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-800.1819673469388</v>
+        <v>-815.2260073469388</v>
       </c>
       <c r="Q92">
-        <v>-439.8819673469388</v>
+        <v>-454.9260073469388</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.19481326096054</v>
+        <v>1.322481401067267</v>
       </c>
       <c r="T92">
-        <v>9.84219909265296</v>
+        <v>10.9357767696144</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4090077699674211</v>
+        <v>0.4045131790886581</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.333601326096054</v>
+        <v>0.335501326096054</v>
       </c>
       <c r="C93">
-        <v>-2844.363428108319</v>
+        <v>-2926.406732541251</v>
       </c>
       <c r="D93">
-        <v>2781.636571891681</v>
+        <v>2763.393267458749</v>
       </c>
       <c r="E93">
-        <v>4306</v>
+        <v>4369.8</v>
       </c>
       <c r="F93">
-        <v>5805.8</v>
+        <v>5869.6</v>
       </c>
       <c r="G93">
         <v>179.8</v>
@@ -8907,28 +8907,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M93">
-        <v>1369.00764</v>
+        <v>1384.05168</v>
       </c>
       <c r="N93">
-        <v>-815.2260073469388</v>
+        <v>-830.2700473469388</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-815.2260073469388</v>
+        <v>-830.2700473469388</v>
       </c>
       <c r="Q93">
-        <v>-454.9260073469388</v>
+        <v>-469.9700473469388</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.322481401067267</v>
+        <v>1.482066576200675</v>
       </c>
       <c r="T93">
-        <v>10.9357767696144</v>
+        <v>12.30274886581621</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4045131790886581</v>
+        <v>0.4001162967072597</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.335501326096054</v>
+        <v>0.337401326096054</v>
       </c>
       <c r="C94">
-        <v>-2926.406732541251</v>
+        <v>-3008.212299520196</v>
       </c>
       <c r="D94">
-        <v>2763.393267458749</v>
+        <v>2745.387700479804</v>
       </c>
       <c r="E94">
-        <v>4369.8</v>
+        <v>4433.6</v>
       </c>
       <c r="F94">
-        <v>5869.6</v>
+        <v>5933.400000000001</v>
       </c>
       <c r="G94">
         <v>179.8</v>
@@ -8989,28 +8989,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M94">
-        <v>1384.05168</v>
+        <v>1399.09572</v>
       </c>
       <c r="N94">
-        <v>-830.2700473469388</v>
+        <v>-845.314087346939</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-830.2700473469388</v>
+        <v>-845.314087346939</v>
       </c>
       <c r="Q94">
-        <v>-469.9700473469388</v>
+        <v>-485.014087346939</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.482066576200675</v>
+        <v>1.687247515657915</v>
       </c>
       <c r="T94">
-        <v>12.30274886581621</v>
+        <v>14.06028441807567</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4001162967072597</v>
+        <v>0.3958139709362138</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.337401326096054</v>
+        <v>0.339301326096054</v>
       </c>
       <c r="C95">
-        <v>-3008.212299520196</v>
+        <v>-3089.784746071952</v>
       </c>
       <c r="D95">
-        <v>2745.387700479804</v>
+        <v>2727.615253928049</v>
       </c>
       <c r="E95">
-        <v>4433.6</v>
+        <v>4497.400000000001</v>
       </c>
       <c r="F95">
-        <v>5933.400000000001</v>
+        <v>5997.200000000001</v>
       </c>
       <c r="G95">
         <v>179.8</v>
@@ -9071,28 +9071,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M95">
-        <v>1399.09572</v>
+        <v>1414.13976</v>
       </c>
       <c r="N95">
-        <v>-845.314087346939</v>
+        <v>-860.358127346939</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-845.314087346939</v>
+        <v>-860.358127346939</v>
       </c>
       <c r="Q95">
-        <v>-485.014087346939</v>
+        <v>-500.058127346939</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.687247515657915</v>
+        <v>1.960822101600901</v>
       </c>
       <c r="T95">
-        <v>14.06028441807567</v>
+        <v>16.40366515442161</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3958139709362138</v>
+        <v>0.3916031840113605</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.339301326096054</v>
+        <v>0.341201326096054</v>
       </c>
       <c r="C96">
-        <v>-3089.784746071952</v>
+        <v>-3171.128570437784</v>
       </c>
       <c r="D96">
-        <v>2727.615253928049</v>
+        <v>2710.071429562216</v>
       </c>
       <c r="E96">
-        <v>4497.400000000001</v>
+        <v>4561.2</v>
       </c>
       <c r="F96">
-        <v>5997.200000000001</v>
+        <v>6061</v>
       </c>
       <c r="G96">
         <v>179.8</v>
@@ -9153,28 +9153,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M96">
-        <v>1414.13976</v>
+        <v>1429.1838</v>
       </c>
       <c r="N96">
-        <v>-860.358127346939</v>
+        <v>-875.4021673469388</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-860.358127346939</v>
+        <v>-875.4021673469388</v>
       </c>
       <c r="Q96">
-        <v>-500.058127346939</v>
+        <v>-515.1021673469388</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.960822101600901</v>
+        <v>2.343826521921082</v>
       </c>
       <c r="T96">
-        <v>16.40366515442161</v>
+        <v>19.68439818530594</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3916031840113605</v>
+        <v>0.3874810452322935</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.341201326096054</v>
+        <v>0.3431013260960539</v>
       </c>
       <c r="C97">
-        <v>-3171.128570437784</v>
+        <v>-3252.248155869113</v>
       </c>
       <c r="D97">
-        <v>2710.071429562216</v>
+        <v>2692.751844130887</v>
       </c>
       <c r="E97">
-        <v>4561.2</v>
+        <v>4625</v>
       </c>
       <c r="F97">
-        <v>6061</v>
+        <v>6124.8</v>
       </c>
       <c r="G97">
         <v>179.8</v>
@@ -9235,28 +9235,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M97">
-        <v>1429.1838</v>
+        <v>1444.22784</v>
       </c>
       <c r="N97">
-        <v>-875.4021673469388</v>
+        <v>-890.4462073469388</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-875.4021673469388</v>
+        <v>-890.4462073469388</v>
       </c>
       <c r="Q97">
-        <v>-515.1021673469388</v>
+        <v>-530.1462073469388</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.343826521921082</v>
+        <v>2.918333152401354</v>
       </c>
       <c r="T97">
-        <v>19.68439818530594</v>
+        <v>24.60549773163244</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3874810452322935</v>
+        <v>0.3834447843444572</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3431013260960539</v>
+        <v>0.3450013260960539</v>
       </c>
       <c r="C98">
-        <v>-3252.248155869113</v>
+        <v>-3333.147774278579</v>
       </c>
       <c r="D98">
-        <v>2692.751844130887</v>
+        <v>2675.652225721421</v>
       </c>
       <c r="E98">
-        <v>4625</v>
+        <v>4688.799999999999</v>
       </c>
       <c r="F98">
-        <v>6124.8</v>
+        <v>6188.599999999999</v>
       </c>
       <c r="G98">
         <v>179.8</v>
@@ -9317,28 +9317,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M98">
-        <v>1444.22784</v>
+        <v>1459.27188</v>
       </c>
       <c r="N98">
-        <v>-890.4462073469388</v>
+        <v>-905.4902473469388</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-890.4462073469388</v>
+        <v>-905.4902473469388</v>
       </c>
       <c r="Q98">
-        <v>-530.1462073469388</v>
+        <v>-545.1902473469388</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.918333152401346</v>
+        <v>3.875844203201795</v>
       </c>
       <c r="T98">
-        <v>24.60549773163238</v>
+        <v>32.80733030884317</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3834447843444572</v>
+        <v>0.3794917453305968</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3450013260960539</v>
+        <v>0.346901326096054</v>
       </c>
       <c r="C99">
-        <v>-3333.147774278579</v>
+        <v>-3413.831589752872</v>
       </c>
       <c r="D99">
-        <v>2675.652225721421</v>
+        <v>2658.768410247128</v>
       </c>
       <c r="E99">
-        <v>4688.799999999999</v>
+        <v>4752.599999999999</v>
       </c>
       <c r="F99">
-        <v>6188.599999999999</v>
+        <v>6252.4</v>
       </c>
       <c r="G99">
         <v>179.8</v>
@@ -9399,28 +9399,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M99">
-        <v>1459.27188</v>
+        <v>1474.31592</v>
       </c>
       <c r="N99">
-        <v>-905.4902473469388</v>
+        <v>-920.5342873469388</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-905.4902473469388</v>
+        <v>-920.5342873469388</v>
       </c>
       <c r="Q99">
-        <v>-545.1902473469388</v>
+        <v>-560.2342873469388</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.875844203201795</v>
+        <v>5.790866304802692</v>
       </c>
       <c r="T99">
-        <v>32.80733030884317</v>
+        <v>49.21099546326475</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3794917453305968</v>
+        <v>0.3756193805823255</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.346901326096054</v>
+        <v>0.348801326096054</v>
       </c>
       <c r="C100">
-        <v>-3413.831589752872</v>
+        <v>-3494.303661933402</v>
       </c>
       <c r="D100">
-        <v>2658.768410247128</v>
+        <v>2642.096338066598</v>
       </c>
       <c r="E100">
-        <v>4752.599999999999</v>
+        <v>4816.4</v>
       </c>
       <c r="F100">
-        <v>6252.4</v>
+        <v>6316.2</v>
       </c>
       <c r="G100">
         <v>179.8</v>
@@ -9481,28 +9481,28 @@
         <v>553.7816326530613</v>
       </c>
       <c r="M100">
-        <v>1474.31592</v>
+        <v>1489.35996</v>
       </c>
       <c r="N100">
-        <v>-920.5342873469388</v>
+        <v>-935.5783273469387</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-920.5342873469388</v>
+        <v>-935.5783273469387</v>
       </c>
       <c r="Q100">
-        <v>-560.2342873469388</v>
+        <v>-575.2783273469388</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.790866304802692</v>
+        <v>11.53593260960538</v>
       </c>
       <c r="T100">
-        <v>49.21099546326475</v>
+        <v>98.4219909265295</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3756193805823255</v>
+        <v>0.3718252454249282</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.348801326096054</v>
-      </c>
-      <c r="C101">
-        <v>-3494.303661933402</v>
-      </c>
-      <c r="D101">
-        <v>2642.096338066598</v>
-      </c>
-      <c r="E101">
-        <v>4816.4</v>
-      </c>
-      <c r="F101">
-        <v>6316.2</v>
-      </c>
-      <c r="G101">
-        <v>179.8</v>
-      </c>
-      <c r="H101">
-        <v>4880.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>914.0816326530612</v>
-      </c>
-      <c r="K101">
-        <v>360.3</v>
-      </c>
-      <c r="L101">
-        <v>553.7816326530613</v>
-      </c>
-      <c r="M101">
-        <v>1489.35996</v>
-      </c>
-      <c r="N101">
-        <v>-935.5783273469387</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-935.5783273469387</v>
-      </c>
-      <c r="Q101">
-        <v>-575.2783273469388</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.53593260960538</v>
-      </c>
-      <c r="T101">
-        <v>98.4219909265295</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3718252454249282</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
